--- a/Asistencias/Asistencias_General.xlsx
+++ b/Asistencias/Asistencias_General.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlosmartinez/Proyectos/Github/CalculoDiferencialTNM/Asistencias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357B6782-CBB4-F546-B2D6-D3CFFBDB1D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6958DAB-90C7-1644-84F2-A2DA4355CB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17020" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M13_CI" sheetId="7" r:id="rId1"/>
@@ -3997,6 +3997,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4050,9 +4053,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4506,9 +4506,9 @@
       <c r="F3" s="26" t="s">
         <v>939</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="33"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="34"/>
       <c r="J3" s="26"/>
       <c r="K3" s="26"/>
       <c r="L3" s="30">
@@ -4564,9 +4564,9 @@
       <c r="F4" s="9" t="s">
         <v>935</v>
       </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="36"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="37"/>
       <c r="J4" s="9">
         <v>1</v>
       </c>
@@ -4656,9 +4656,9 @@
       <c r="F5" s="7" t="s">
         <v>931</v>
       </c>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="36"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="37"/>
       <c r="J5" s="7">
         <v>1</v>
       </c>
@@ -4748,9 +4748,9 @@
       <c r="F6" s="9" t="s">
         <v>927</v>
       </c>
-      <c r="G6" s="34"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="36"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="37"/>
       <c r="J6" s="9"/>
       <c r="K6" s="9">
         <v>1</v>
@@ -4840,9 +4840,9 @@
       <c r="F7" s="7" t="s">
         <v>922</v>
       </c>
-      <c r="G7" s="34"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="36"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="37"/>
       <c r="J7" s="7">
         <v>1</v>
       </c>
@@ -4934,9 +4934,9 @@
       <c r="F8" s="9" t="s">
         <v>918</v>
       </c>
-      <c r="G8" s="34"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="36"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="37"/>
       <c r="J8" s="9">
         <v>1</v>
       </c>
@@ -5024,9 +5024,9 @@
       <c r="F9" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="G9" s="34"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="36"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="37"/>
       <c r="J9" s="7">
         <v>1</v>
       </c>
@@ -5118,9 +5118,9 @@
       <c r="F10" s="9" t="s">
         <v>910</v>
       </c>
-      <c r="G10" s="34"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="36"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="37"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="13">
@@ -5202,9 +5202,9 @@
       <c r="F11" s="7" t="s">
         <v>906</v>
       </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="36"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="37"/>
       <c r="J11" s="7">
         <v>1</v>
       </c>
@@ -5294,9 +5294,9 @@
       <c r="F12" s="9" t="s">
         <v>902</v>
       </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="36"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="37"/>
       <c r="J12" s="9"/>
       <c r="K12" s="9">
         <v>1</v>
@@ -5382,9 +5382,9 @@
       <c r="F13" s="26" t="s">
         <v>898</v>
       </c>
-      <c r="G13" s="34"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="36"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="37"/>
       <c r="J13" s="26"/>
       <c r="K13" s="26"/>
       <c r="L13" s="30">
@@ -5440,9 +5440,9 @@
       <c r="F14" s="9" t="s">
         <v>894</v>
       </c>
-      <c r="G14" s="34"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="36"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="37"/>
       <c r="J14" s="9">
         <v>1</v>
       </c>
@@ -5528,9 +5528,9 @@
       <c r="F15" s="7" t="s">
         <v>890</v>
       </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="36"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="37"/>
       <c r="J15" s="7">
         <v>1</v>
       </c>
@@ -5622,9 +5622,9 @@
       <c r="F16" s="26" t="s">
         <v>886</v>
       </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="36"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="37"/>
       <c r="J16" s="26"/>
       <c r="K16" s="26"/>
       <c r="L16" s="30">
@@ -5680,9 +5680,9 @@
       <c r="F17" s="7" t="s">
         <v>882</v>
       </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="36"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="37"/>
       <c r="J17" s="7">
         <v>1</v>
       </c>
@@ -5770,9 +5770,9 @@
       <c r="F18" s="9" t="s">
         <v>878</v>
       </c>
-      <c r="G18" s="34"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="36"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="37"/>
       <c r="J18" s="9">
         <v>1</v>
       </c>
@@ -5862,9 +5862,9 @@
       <c r="F19" s="7" t="s">
         <v>874</v>
       </c>
-      <c r="G19" s="34"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="36"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="37"/>
       <c r="J19" s="7">
         <v>1</v>
       </c>
@@ -5954,9 +5954,9 @@
       <c r="F20" s="9" t="s">
         <v>870</v>
       </c>
-      <c r="G20" s="34"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="36"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="37"/>
       <c r="J20" s="9">
         <v>1</v>
       </c>
@@ -6044,9 +6044,9 @@
       <c r="F21" s="7" t="s">
         <v>866</v>
       </c>
-      <c r="G21" s="34"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="36"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="37"/>
       <c r="J21" s="7">
         <v>1</v>
       </c>
@@ -6136,9 +6136,9 @@
       <c r="F22" s="9" t="s">
         <v>862</v>
       </c>
-      <c r="G22" s="34"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="36"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="37"/>
       <c r="J22" s="9">
         <v>1</v>
       </c>
@@ -6226,9 +6226,9 @@
       <c r="F23" s="7" t="s">
         <v>858</v>
       </c>
-      <c r="G23" s="34"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="36"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="37"/>
       <c r="J23" s="7">
         <v>1</v>
       </c>
@@ -6316,9 +6316,9 @@
       <c r="F24" s="9" t="s">
         <v>854</v>
       </c>
-      <c r="G24" s="34"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="36"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="37"/>
       <c r="J24" s="9">
         <v>1</v>
       </c>
@@ -6408,9 +6408,9 @@
       <c r="F25" s="26" t="s">
         <v>850</v>
       </c>
-      <c r="G25" s="34"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="36"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="37"/>
       <c r="J25" s="26">
         <v>1</v>
       </c>
@@ -6470,9 +6470,9 @@
       <c r="F26" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="G26" s="34"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="36"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="37"/>
       <c r="J26" s="9">
         <v>1</v>
       </c>
@@ -6562,9 +6562,9 @@
       <c r="F27" s="7" t="s">
         <v>842</v>
       </c>
-      <c r="G27" s="34"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="36"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="37"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
       <c r="L27" s="12">
@@ -6650,9 +6650,9 @@
       <c r="F28" s="9" t="s">
         <v>838</v>
       </c>
-      <c r="G28" s="34"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="36"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="37"/>
       <c r="J28" s="9">
         <v>1</v>
       </c>
@@ -6736,9 +6736,9 @@
       <c r="F29" s="7" t="s">
         <v>834</v>
       </c>
-      <c r="G29" s="34"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="36"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="37"/>
       <c r="J29" s="7">
         <v>1</v>
       </c>
@@ -6826,9 +6826,9 @@
       <c r="F30" s="9" t="s">
         <v>830</v>
       </c>
-      <c r="G30" s="34"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="36"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="37"/>
       <c r="J30" s="9">
         <v>1</v>
       </c>
@@ -6918,9 +6918,9 @@
       <c r="F31" s="7" t="s">
         <v>826</v>
       </c>
-      <c r="G31" s="34"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="36"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="37"/>
       <c r="J31" s="7"/>
       <c r="K31" s="7">
         <v>1</v>
@@ -7008,9 +7008,9 @@
       <c r="F32" s="26" t="s">
         <v>822</v>
       </c>
-      <c r="G32" s="34"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="36"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="37"/>
       <c r="J32" s="26"/>
       <c r="K32" s="26"/>
       <c r="L32" s="26"/>
@@ -7072,9 +7072,9 @@
       <c r="F33" s="26" t="s">
         <v>818</v>
       </c>
-      <c r="G33" s="34"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="36"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="37"/>
       <c r="J33" s="26"/>
       <c r="K33" s="26"/>
       <c r="L33" s="30">
@@ -7130,9 +7130,9 @@
       <c r="F34" s="9" t="s">
         <v>814</v>
       </c>
-      <c r="G34" s="34"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="36"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="37"/>
       <c r="J34" s="9">
         <v>1</v>
       </c>
@@ -7204,9 +7204,9 @@
       <c r="F35" s="7" t="s">
         <v>810</v>
       </c>
-      <c r="G35" s="34"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="36"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="37"/>
       <c r="J35" s="7"/>
       <c r="K35" s="7">
         <v>1</v>
@@ -7280,9 +7280,9 @@
       <c r="F36" s="9" t="s">
         <v>806</v>
       </c>
-      <c r="G36" s="37"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="39"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="40"/>
       <c r="J36" s="9">
         <v>1</v>
       </c>
@@ -7505,8 +7505,8 @@
       <c r="F3" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="33"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="34"/>
       <c r="I3" s="7">
         <v>1</v>
       </c>
@@ -7601,8 +7601,8 @@
       <c r="F4" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="36"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="37"/>
       <c r="I4" s="9">
         <v>1</v>
       </c>
@@ -7693,8 +7693,8 @@
       <c r="F5" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="G5" s="34"/>
-      <c r="H5" s="36"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="37"/>
       <c r="I5" s="7">
         <v>1</v>
       </c>
@@ -7785,8 +7785,8 @@
       <c r="F6" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="G6" s="34"/>
-      <c r="H6" s="36"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="37"/>
       <c r="I6" s="9">
         <v>1</v>
       </c>
@@ -7879,8 +7879,8 @@
       <c r="F7" s="26" t="s">
         <v>412</v>
       </c>
-      <c r="G7" s="34"/>
-      <c r="H7" s="36"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="37"/>
       <c r="I7" s="26"/>
       <c r="J7" s="26"/>
       <c r="K7" s="26"/>
@@ -7935,8 +7935,8 @@
       <c r="F8" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="G8" s="34"/>
-      <c r="H8" s="36"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="37"/>
       <c r="I8" s="9">
         <v>1</v>
       </c>
@@ -8023,8 +8023,8 @@
       <c r="F9" s="26" t="s">
         <v>404</v>
       </c>
-      <c r="G9" s="34"/>
-      <c r="H9" s="36"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="37"/>
       <c r="I9" s="26"/>
       <c r="J9" s="26"/>
       <c r="K9" s="26"/>
@@ -8079,8 +8079,8 @@
       <c r="F10" s="26" t="s">
         <v>400</v>
       </c>
-      <c r="G10" s="34"/>
-      <c r="H10" s="36"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="37"/>
       <c r="I10" s="26"/>
       <c r="J10" s="26"/>
       <c r="K10" s="26">
@@ -8139,8 +8139,8 @@
       <c r="F11" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="36"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="37"/>
       <c r="I11" s="7">
         <v>1</v>
       </c>
@@ -8233,8 +8233,8 @@
       <c r="F12" s="26" t="s">
         <v>392</v>
       </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="36"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="26"/>
       <c r="J12" s="26"/>
       <c r="K12" s="26"/>
@@ -8291,8 +8291,8 @@
       <c r="F13" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="G13" s="34"/>
-      <c r="H13" s="36"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
@@ -8337,7 +8337,7 @@
       <c r="B14" s="9">
         <v>1</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="31" t="s">
         <v>386</v>
       </c>
       <c r="D14" s="9" t="s">
@@ -8349,8 +8349,8 @@
       <c r="F14" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="G14" s="34"/>
-      <c r="H14" s="36"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="37"/>
       <c r="I14" s="9">
         <v>1</v>
       </c>
@@ -8445,8 +8445,8 @@
       <c r="F15" s="26" t="s">
         <v>380</v>
       </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="36"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="37"/>
       <c r="I15" s="26"/>
       <c r="J15" s="26"/>
       <c r="K15" s="26"/>
@@ -8501,8 +8501,8 @@
       <c r="F16" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="36"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="37"/>
       <c r="I16" s="9">
         <v>1</v>
       </c>
@@ -8587,8 +8587,8 @@
       <c r="F17" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="36"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="37"/>
       <c r="I17" s="7">
         <v>1</v>
       </c>
@@ -8669,7 +8669,7 @@
       <c r="B18" s="9">
         <v>1</v>
       </c>
-      <c r="C18" s="49" t="s">
+      <c r="C18" s="31" t="s">
         <v>369</v>
       </c>
       <c r="D18" s="9" t="s">
@@ -8681,8 +8681,8 @@
       <c r="F18" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="G18" s="34"/>
-      <c r="H18" s="36"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="37"/>
       <c r="I18" s="9">
         <v>1</v>
       </c>
@@ -8773,8 +8773,8 @@
       <c r="F19" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="G19" s="34"/>
-      <c r="H19" s="36"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="37"/>
       <c r="I19" s="7">
         <v>1</v>
       </c>
@@ -8863,8 +8863,8 @@
       <c r="F20" s="26" t="s">
         <v>358</v>
       </c>
-      <c r="G20" s="34"/>
-      <c r="H20" s="36"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="37"/>
       <c r="I20" s="26"/>
       <c r="J20" s="26"/>
       <c r="K20" s="26"/>
@@ -8919,8 +8919,8 @@
       <c r="F21" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="G21" s="34"/>
-      <c r="H21" s="36"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="37"/>
       <c r="I21" s="7">
         <v>1</v>
       </c>
@@ -9011,8 +9011,8 @@
       <c r="F22" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="G22" s="34"/>
-      <c r="H22" s="36"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="37"/>
       <c r="I22" s="9">
         <v>1</v>
       </c>
@@ -9107,8 +9107,8 @@
       <c r="F23" s="26" t="s">
         <v>346</v>
       </c>
-      <c r="G23" s="34"/>
-      <c r="H23" s="36"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="37"/>
       <c r="I23" s="26">
         <v>1</v>
       </c>
@@ -9191,8 +9191,8 @@
       <c r="F24" s="26" t="s">
         <v>342</v>
       </c>
-      <c r="G24" s="34"/>
-      <c r="H24" s="36"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="37"/>
       <c r="I24" s="26">
         <v>1</v>
       </c>
@@ -9279,8 +9279,8 @@
       <c r="F25" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="G25" s="34"/>
-      <c r="H25" s="36"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="37"/>
       <c r="I25" s="26"/>
       <c r="J25" s="26"/>
       <c r="K25" s="26"/>
@@ -9335,8 +9335,8 @@
       <c r="F26" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="G26" s="34"/>
-      <c r="H26" s="36"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="37"/>
       <c r="I26" s="9">
         <v>1</v>
       </c>
@@ -9427,8 +9427,8 @@
       <c r="F27" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="G27" s="34"/>
-      <c r="H27" s="36"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="37"/>
       <c r="I27" s="7">
         <v>1</v>
       </c>
@@ -9523,8 +9523,8 @@
       <c r="F28" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="G28" s="34"/>
-      <c r="H28" s="36"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="37"/>
       <c r="I28" s="9">
         <v>1</v>
       </c>
@@ -9613,8 +9613,8 @@
       <c r="F29" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="G29" s="34"/>
-      <c r="H29" s="36"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="37"/>
       <c r="I29" s="7">
         <v>1</v>
       </c>
@@ -9707,8 +9707,8 @@
       <c r="F30" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="G30" s="34"/>
-      <c r="H30" s="36"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="37"/>
       <c r="I30" s="9"/>
       <c r="J30" s="9">
         <v>1</v>
@@ -9785,8 +9785,8 @@
       <c r="F31" s="26" t="s">
         <v>311</v>
       </c>
-      <c r="G31" s="34"/>
-      <c r="H31" s="36"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="37"/>
       <c r="I31" s="26"/>
       <c r="J31" s="26"/>
       <c r="K31" s="26"/>
@@ -9841,8 +9841,8 @@
       <c r="F32" s="26" t="s">
         <v>307</v>
       </c>
-      <c r="G32" s="34"/>
-      <c r="H32" s="36"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="37"/>
       <c r="I32" s="26"/>
       <c r="J32" s="26"/>
       <c r="K32" s="26"/>
@@ -9897,8 +9897,8 @@
       <c r="F33" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="G33" s="34"/>
-      <c r="H33" s="36"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="37"/>
       <c r="I33" s="7">
         <v>1</v>
       </c>
@@ -9987,8 +9987,8 @@
       <c r="F34" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="G34" s="34"/>
-      <c r="H34" s="36"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="37"/>
       <c r="I34" s="26">
         <v>1</v>
       </c>
@@ -10071,8 +10071,8 @@
       <c r="F35" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="G35" s="34"/>
-      <c r="H35" s="36"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="37"/>
       <c r="I35" s="26"/>
       <c r="J35" s="26"/>
       <c r="K35" s="26"/>
@@ -10127,8 +10127,8 @@
       <c r="F36" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="G36" s="37"/>
-      <c r="H36" s="39"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="40"/>
       <c r="I36" s="9">
         <v>1</v>
       </c>
@@ -10353,9 +10353,9 @@
       <c r="F3" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="33"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="34"/>
       <c r="J3" s="7">
         <v>1</v>
       </c>
@@ -10445,9 +10445,9 @@
       <c r="F4" s="9" t="s">
         <v>573</v>
       </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="36"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="37"/>
       <c r="J4" s="9"/>
       <c r="K4" s="9">
         <v>1</v>
@@ -10513,9 +10513,9 @@
       <c r="F5" s="7" t="s">
         <v>569</v>
       </c>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="36"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="37"/>
       <c r="J5" s="7">
         <v>1</v>
       </c>
@@ -10583,9 +10583,9 @@
       <c r="F6" s="9" t="s">
         <v>565</v>
       </c>
-      <c r="G6" s="34"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="36"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="37"/>
       <c r="J6" s="9">
         <v>1</v>
       </c>
@@ -10653,9 +10653,9 @@
       <c r="F7" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="G7" s="34"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="36"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="37"/>
       <c r="J7" s="7">
         <v>1</v>
       </c>
@@ -10723,9 +10723,9 @@
       <c r="F8" s="9" t="s">
         <v>557</v>
       </c>
-      <c r="G8" s="34"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="36"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="37"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
@@ -10779,9 +10779,9 @@
       <c r="F9" s="7" t="s">
         <v>553</v>
       </c>
-      <c r="G9" s="34"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="36"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="37"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
@@ -10835,9 +10835,9 @@
       <c r="F10" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="G10" s="34"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="36"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="37"/>
       <c r="J10" s="9">
         <v>1</v>
       </c>
@@ -10905,9 +10905,9 @@
       <c r="F11" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="36"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="37"/>
       <c r="J11" s="7">
         <v>1</v>
       </c>
@@ -10975,9 +10975,9 @@
       <c r="F12" s="9" t="s">
         <v>541</v>
       </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="36"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="37"/>
       <c r="J12" s="9">
         <v>1</v>
       </c>
@@ -11045,9 +11045,9 @@
       <c r="F13" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="G13" s="34"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="36"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="37"/>
       <c r="J13" s="7">
         <v>1</v>
       </c>
@@ -11115,9 +11115,9 @@
       <c r="F14" s="9" t="s">
         <v>533</v>
       </c>
-      <c r="G14" s="34"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="36"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="37"/>
       <c r="J14" s="9">
         <v>1</v>
       </c>
@@ -11185,9 +11185,9 @@
       <c r="F15" s="7" t="s">
         <v>529</v>
       </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="36"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="37"/>
       <c r="J15" s="7">
         <v>1</v>
       </c>
@@ -11255,9 +11255,9 @@
       <c r="F16" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="36"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="37"/>
       <c r="J16" s="9">
         <v>1</v>
       </c>
@@ -11325,9 +11325,9 @@
       <c r="F17" s="7" t="s">
         <v>521</v>
       </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="36"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="37"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7">
@@ -11383,9 +11383,9 @@
       <c r="F18" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="G18" s="34"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="36"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="37"/>
       <c r="J18" s="9">
         <v>1</v>
       </c>
@@ -11453,9 +11453,9 @@
       <c r="F19" s="7" t="s">
         <v>513</v>
       </c>
-      <c r="G19" s="34"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="36"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="37"/>
       <c r="J19" s="7">
         <v>1</v>
       </c>
@@ -11517,9 +11517,9 @@
       <c r="F20" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="G20" s="34"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="36"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="37"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
@@ -11573,9 +11573,9 @@
       <c r="F21" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="G21" s="34"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="36"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="37"/>
       <c r="J21" s="7">
         <v>1</v>
       </c>
@@ -11643,9 +11643,9 @@
       <c r="F22" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="G22" s="34"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="36"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="37"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
@@ -11699,9 +11699,9 @@
       <c r="F23" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="G23" s="34"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="36"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="37"/>
       <c r="J23" s="7">
         <v>1</v>
       </c>
@@ -11763,9 +11763,9 @@
       <c r="F24" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="G24" s="34"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="36"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="37"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="9">
@@ -11821,9 +11821,9 @@
       <c r="F25" s="7" t="s">
         <v>489</v>
       </c>
-      <c r="G25" s="34"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="36"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="37"/>
       <c r="J25" s="7">
         <v>1</v>
       </c>
@@ -11891,9 +11891,9 @@
       <c r="F26" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="G26" s="34"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="36"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="37"/>
       <c r="J26" s="9">
         <v>1</v>
       </c>
@@ -11961,9 +11961,9 @@
       <c r="F27" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="G27" s="34"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="36"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="37"/>
       <c r="J27" s="7">
         <v>1</v>
       </c>
@@ -12031,9 +12031,9 @@
       <c r="F28" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="G28" s="34"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="36"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="37"/>
       <c r="J28" s="9">
         <v>1</v>
       </c>
@@ -12123,9 +12123,9 @@
       <c r="F29" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="G29" s="34"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="36"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="37"/>
       <c r="J29" s="7">
         <v>1</v>
       </c>
@@ -12193,9 +12193,9 @@
       <c r="F30" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="G30" s="34"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="36"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="37"/>
       <c r="J30" s="9">
         <v>1</v>
       </c>
@@ -12263,9 +12263,9 @@
       <c r="F31" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="G31" s="34"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="36"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="37"/>
       <c r="J31" s="7">
         <v>1</v>
       </c>
@@ -12333,9 +12333,9 @@
       <c r="F32" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="G32" s="34"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="36"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="37"/>
       <c r="J32" s="9">
         <v>1</v>
       </c>
@@ -12403,9 +12403,9 @@
       <c r="F33" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="G33" s="34"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="36"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="37"/>
       <c r="J33" s="7">
         <v>1</v>
       </c>
@@ -12473,9 +12473,9 @@
       <c r="F34" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="G34" s="34"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="36"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="37"/>
       <c r="J34" s="9">
         <v>1</v>
       </c>
@@ -12543,9 +12543,9 @@
       <c r="F35" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="G35" s="34"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="36"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="37"/>
       <c r="J35" s="7">
         <v>1</v>
       </c>
@@ -12613,9 +12613,9 @@
       <c r="F36" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="G36" s="34"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="36"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="37"/>
       <c r="J36" s="9">
         <v>1</v>
       </c>
@@ -12699,9 +12699,9 @@
       <c r="F37" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="G37" s="34"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="36"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="37"/>
       <c r="J37" s="7">
         <v>1</v>
       </c>
@@ -12769,9 +12769,9 @@
       <c r="F38" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="G38" s="34"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="36"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="37"/>
       <c r="J38" s="9">
         <v>1</v>
       </c>
@@ -12839,9 +12839,9 @@
       <c r="F39" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="G39" s="37"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="39"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="40"/>
       <c r="J39" s="7">
         <v>1</v>
       </c>
@@ -13066,9 +13066,9 @@
       <c r="F3" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="33"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="34"/>
       <c r="J3" s="7">
         <v>1</v>
       </c>
@@ -13162,9 +13162,9 @@
       <c r="F4" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="36"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="37"/>
       <c r="J4" s="9">
         <v>1</v>
       </c>
@@ -13258,9 +13258,9 @@
       <c r="F5" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="36"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="37"/>
       <c r="J5" s="7">
         <v>1</v>
       </c>
@@ -13352,9 +13352,9 @@
       <c r="F6" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="G6" s="34"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="36"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="37"/>
       <c r="J6" s="9">
         <v>1</v>
       </c>
@@ -13448,9 +13448,9 @@
       <c r="F7" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="G7" s="34"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="36"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="37"/>
       <c r="J7" s="7">
         <v>1</v>
       </c>
@@ -13544,9 +13544,9 @@
       <c r="F8" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="G8" s="34"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="36"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="37"/>
       <c r="J8" s="9">
         <v>1</v>
       </c>
@@ -13640,9 +13640,9 @@
       <c r="F9" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="G9" s="34"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="36"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="37"/>
       <c r="J9" s="7">
         <v>1</v>
       </c>
@@ -13736,9 +13736,9 @@
       <c r="F10" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="G10" s="34"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="36"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="37"/>
       <c r="J10" s="9">
         <v>1</v>
       </c>
@@ -13832,9 +13832,9 @@
       <c r="F11" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="36"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="37"/>
       <c r="J11" s="7">
         <v>1</v>
       </c>
@@ -13928,9 +13928,9 @@
       <c r="F12" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="36"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="37"/>
       <c r="J12" s="9">
         <v>1</v>
       </c>
@@ -14022,9 +14022,9 @@
       <c r="F13" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="G13" s="34"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="36"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="37"/>
       <c r="J13" s="7">
         <v>1</v>
       </c>
@@ -14118,9 +14118,9 @@
       <c r="F14" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="G14" s="34"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="36"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="37"/>
       <c r="J14" s="9">
         <v>1</v>
       </c>
@@ -14214,9 +14214,9 @@
       <c r="F15" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="36"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="37"/>
       <c r="J15" s="7">
         <v>1</v>
       </c>
@@ -14310,9 +14310,9 @@
       <c r="F16" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="36"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="37"/>
       <c r="J16" s="9">
         <v>1</v>
       </c>
@@ -14406,9 +14406,9 @@
       <c r="F17" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="36"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="37"/>
       <c r="J17" s="7">
         <v>1</v>
       </c>
@@ -14500,9 +14500,9 @@
       <c r="F18" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="G18" s="34"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="36"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="37"/>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
@@ -14560,9 +14560,9 @@
       <c r="F19" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="G19" s="34"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="36"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="37"/>
       <c r="J19" s="7">
         <v>1</v>
       </c>
@@ -14656,9 +14656,9 @@
       <c r="F20" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="G20" s="34"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="36"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="37"/>
       <c r="J20" s="9">
         <v>1</v>
       </c>
@@ -14752,9 +14752,9 @@
       <c r="F21" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G21" s="34"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="36"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="37"/>
       <c r="J21" s="7">
         <v>1</v>
       </c>
@@ -14848,9 +14848,9 @@
       <c r="F22" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="G22" s="34"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="36"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="37"/>
       <c r="J22" s="9">
         <v>1</v>
       </c>
@@ -14944,9 +14944,9 @@
       <c r="F23" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="G23" s="34"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="36"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="37"/>
       <c r="J23" s="7">
         <v>1</v>
       </c>
@@ -15040,9 +15040,9 @@
       <c r="F24" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="G24" s="34"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="36"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="37"/>
       <c r="J24" s="9">
         <v>1</v>
       </c>
@@ -15136,9 +15136,9 @@
       <c r="F25" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="G25" s="34"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="36"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="37"/>
       <c r="J25" s="7">
         <v>1</v>
       </c>
@@ -15232,9 +15232,9 @@
       <c r="F26" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="G26" s="34"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="36"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="37"/>
       <c r="J26" s="9">
         <v>1</v>
       </c>
@@ -15328,9 +15328,9 @@
       <c r="F27" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G27" s="34"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="36"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="37"/>
       <c r="J27" s="7">
         <v>1</v>
       </c>
@@ -15422,9 +15422,9 @@
       <c r="F28" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="G28" s="34"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="36"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="37"/>
       <c r="J28" s="9">
         <v>1</v>
       </c>
@@ -15496,9 +15496,9 @@
       <c r="F29" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="G29" s="34"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="36"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="37"/>
       <c r="J29" s="7">
         <v>1</v>
       </c>
@@ -15588,9 +15588,9 @@
       <c r="F30" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="G30" s="34"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="36"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="37"/>
       <c r="J30" s="9">
         <v>1</v>
       </c>
@@ -15684,9 +15684,9 @@
       <c r="F31" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="G31" s="34"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="36"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="37"/>
       <c r="J31" s="7">
         <v>1</v>
       </c>
@@ -15780,9 +15780,9 @@
       <c r="F32" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="G32" s="34"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="36"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="37"/>
       <c r="J32" s="9">
         <v>1</v>
       </c>
@@ -15876,9 +15876,9 @@
       <c r="F33" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="G33" s="34"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="36"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="37"/>
       <c r="J33" s="7">
         <v>1</v>
       </c>
@@ -15970,9 +15970,9 @@
       <c r="F34" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="G34" s="34"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="36"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="37"/>
       <c r="J34" s="9">
         <v>1</v>
       </c>
@@ -16062,9 +16062,9 @@
       <c r="F35" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="G35" s="34"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="36"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="37"/>
       <c r="J35" s="7">
         <v>1</v>
       </c>
@@ -16158,9 +16158,9 @@
       <c r="F36" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="G36" s="34"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="36"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="37"/>
       <c r="J36" s="9">
         <v>1</v>
       </c>
@@ -16254,9 +16254,9 @@
       <c r="F37" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="G37" s="34"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="36"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="37"/>
       <c r="J37" s="7">
         <v>1</v>
       </c>
@@ -16350,9 +16350,9 @@
       <c r="F38" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="G38" s="34"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="36"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="37"/>
       <c r="J38" s="9">
         <v>1</v>
       </c>
@@ -16444,9 +16444,9 @@
       <c r="F39" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G39" s="34"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="36"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="37"/>
       <c r="J39" s="7">
         <v>1</v>
       </c>
@@ -16510,9 +16510,9 @@
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="9"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="36"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="37"/>
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
       <c r="L40" s="9"/>
@@ -16832,8 +16832,8 @@
       <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="42"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -16890,8 +16890,8 @@
       <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="42"/>
-      <c r="H4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="44"/>
       <c r="I4" s="3">
         <v>1</v>
       </c>
@@ -16984,8 +16984,8 @@
       <c r="F5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="44"/>
       <c r="I5" s="2">
         <v>1</v>
       </c>
@@ -17078,8 +17078,8 @@
       <c r="F6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="42"/>
-      <c r="H6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
       <c r="I6" s="3">
         <v>1</v>
       </c>
@@ -17172,8 +17172,8 @@
       <c r="F7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="42"/>
-      <c r="H7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="44"/>
       <c r="I7" s="2">
         <v>1</v>
       </c>
@@ -17266,8 +17266,8 @@
       <c r="F8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="42"/>
-      <c r="H8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="44"/>
       <c r="I8" s="3">
         <v>1</v>
       </c>
@@ -17360,8 +17360,8 @@
       <c r="F9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="42"/>
-      <c r="H9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="44"/>
       <c r="I9" s="2">
         <v>1</v>
       </c>
@@ -17454,8 +17454,8 @@
       <c r="F10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="42"/>
-      <c r="H10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="44"/>
       <c r="I10" s="3">
         <v>1</v>
       </c>
@@ -17548,8 +17548,8 @@
       <c r="F11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="42"/>
-      <c r="H11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="44"/>
       <c r="I11" s="2">
         <v>1</v>
       </c>
@@ -17642,8 +17642,8 @@
       <c r="F12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="42"/>
-      <c r="H12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="44"/>
       <c r="I12" s="3">
         <v>1</v>
       </c>
@@ -17728,8 +17728,8 @@
       <c r="F13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="42"/>
-      <c r="H13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="44"/>
       <c r="I13" s="2">
         <v>1</v>
       </c>
@@ -17822,8 +17822,8 @@
       <c r="F14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="42"/>
-      <c r="H14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="44"/>
       <c r="I14" s="3">
         <v>1</v>
       </c>
@@ -17914,8 +17914,8 @@
       <c r="F15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G15" s="42"/>
-      <c r="H15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="44"/>
       <c r="I15" s="2">
         <v>1</v>
       </c>
@@ -18008,8 +18008,8 @@
       <c r="F16" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G16" s="42"/>
-      <c r="H16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="44"/>
       <c r="I16" s="3">
         <v>1</v>
       </c>
@@ -18100,8 +18100,8 @@
       <c r="F17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="42"/>
-      <c r="H17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="44"/>
       <c r="I17" s="2">
         <v>1</v>
       </c>
@@ -18194,8 +18194,8 @@
       <c r="F18" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G18" s="42"/>
-      <c r="H18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="44"/>
       <c r="I18" s="3">
         <v>1</v>
       </c>
@@ -18284,8 +18284,8 @@
       <c r="F19" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G19" s="42"/>
-      <c r="H19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="44"/>
       <c r="I19" s="2">
         <v>1</v>
       </c>
@@ -18378,8 +18378,8 @@
       <c r="F20" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G20" s="42"/>
-      <c r="H20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="44"/>
       <c r="I20" s="3">
         <v>1</v>
       </c>
@@ -18472,8 +18472,8 @@
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G21" s="42"/>
-      <c r="H21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="44"/>
       <c r="I21" s="2">
         <v>1</v>
       </c>
@@ -18566,8 +18566,8 @@
       <c r="F22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G22" s="42"/>
-      <c r="H22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="44"/>
       <c r="I22" s="3">
         <v>1</v>
       </c>
@@ -18660,8 +18660,8 @@
       <c r="F23" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G23" s="42"/>
-      <c r="H23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="44"/>
       <c r="I23" s="2">
         <v>1</v>
       </c>
@@ -18754,8 +18754,8 @@
       <c r="F24" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="G24" s="42"/>
-      <c r="H24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="44"/>
       <c r="I24" s="3">
         <v>1</v>
       </c>
@@ -18848,8 +18848,8 @@
       <c r="F25" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G25" s="42"/>
-      <c r="H25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="44"/>
       <c r="I25" s="2">
         <v>1</v>
       </c>
@@ -18942,8 +18942,8 @@
       <c r="F26" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G26" s="42"/>
-      <c r="H26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="44"/>
       <c r="I26" s="3">
         <v>1</v>
       </c>
@@ -19036,8 +19036,8 @@
       <c r="F27" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G27" s="42"/>
-      <c r="H27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="44"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -19092,8 +19092,8 @@
       <c r="F28" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G28" s="42"/>
-      <c r="H28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="44"/>
       <c r="I28" s="3">
         <v>1</v>
       </c>
@@ -19186,8 +19186,8 @@
       <c r="F29" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G29" s="42"/>
-      <c r="H29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="44"/>
       <c r="I29" s="2">
         <v>1</v>
       </c>
@@ -19280,8 +19280,8 @@
       <c r="F30" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G30" s="42"/>
-      <c r="H30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="44"/>
       <c r="I30" s="3">
         <v>1</v>
       </c>
@@ -19374,8 +19374,8 @@
       <c r="F31" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G31" s="42"/>
-      <c r="H31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="44"/>
       <c r="I31" s="2">
         <v>1</v>
       </c>
@@ -19468,8 +19468,8 @@
       <c r="F32" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G32" s="42"/>
-      <c r="H32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="44"/>
       <c r="I32" s="3">
         <v>1</v>
       </c>
@@ -19562,8 +19562,8 @@
       <c r="F33" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G33" s="42"/>
-      <c r="H33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="44"/>
       <c r="I33" s="2">
         <v>1</v>
       </c>
@@ -19656,8 +19656,8 @@
       <c r="F34" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G34" s="44"/>
-      <c r="H34" s="45"/>
+      <c r="G34" s="45"/>
+      <c r="H34" s="46"/>
       <c r="I34" s="3">
         <v>1</v>
       </c>
@@ -19891,8 +19891,8 @@
       <c r="F3" s="7" t="s">
         <v>1031</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="33"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="34"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
@@ -19947,8 +19947,8 @@
       <c r="F4" s="9" t="s">
         <v>1027</v>
       </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="36"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="37"/>
       <c r="I4" s="9">
         <v>1</v>
       </c>
@@ -20011,8 +20011,8 @@
       <c r="F5" s="7" t="s">
         <v>1023</v>
       </c>
-      <c r="G5" s="34"/>
-      <c r="H5" s="36"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="37"/>
       <c r="I5" s="7">
         <v>1</v>
       </c>
@@ -20075,8 +20075,8 @@
       <c r="F6" s="9" t="s">
         <v>1019</v>
       </c>
-      <c r="G6" s="34"/>
-      <c r="H6" s="36"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="37"/>
       <c r="I6" s="9">
         <v>1</v>
       </c>
@@ -20139,8 +20139,8 @@
       <c r="F7" s="7" t="s">
         <v>1015</v>
       </c>
-      <c r="G7" s="34"/>
-      <c r="H7" s="36"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="37"/>
       <c r="I7" s="7">
         <v>1</v>
       </c>
@@ -20203,8 +20203,8 @@
       <c r="F8" s="9" t="s">
         <v>1011</v>
       </c>
-      <c r="G8" s="34"/>
-      <c r="H8" s="36"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="37"/>
       <c r="I8" s="9">
         <v>1</v>
       </c>
@@ -20267,8 +20267,8 @@
       <c r="F9" s="7" t="s">
         <v>1007</v>
       </c>
-      <c r="G9" s="34"/>
-      <c r="H9" s="36"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="37"/>
       <c r="I9" s="7">
         <v>1</v>
       </c>
@@ -20331,8 +20331,8 @@
       <c r="F10" s="9" t="s">
         <v>1003</v>
       </c>
-      <c r="G10" s="34"/>
-      <c r="H10" s="36"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="37"/>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
@@ -20387,8 +20387,8 @@
       <c r="F11" s="7" t="s">
         <v>999</v>
       </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="36"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="37"/>
       <c r="I11" s="7">
         <v>1</v>
       </c>
@@ -20451,8 +20451,8 @@
       <c r="F12" s="9" t="s">
         <v>995</v>
       </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="36"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="9">
         <v>1</v>
       </c>
@@ -20515,8 +20515,8 @@
       <c r="F13" s="7" t="s">
         <v>991</v>
       </c>
-      <c r="G13" s="34"/>
-      <c r="H13" s="36"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="7">
         <v>1</v>
       </c>
@@ -20579,8 +20579,8 @@
       <c r="F14" s="9" t="s">
         <v>987</v>
       </c>
-      <c r="G14" s="34"/>
-      <c r="H14" s="36"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="37"/>
       <c r="I14" s="9">
         <v>1</v>
       </c>
@@ -20643,8 +20643,8 @@
       <c r="F15" s="7" t="s">
         <v>983</v>
       </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="36"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="37"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
@@ -20699,8 +20699,8 @@
       <c r="F16" s="9" t="s">
         <v>979</v>
       </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="36"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="37"/>
       <c r="I16" s="9">
         <v>1</v>
       </c>
@@ -20763,8 +20763,8 @@
       <c r="F17" s="7" t="s">
         <v>975</v>
       </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="36"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="37"/>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
@@ -20819,8 +20819,8 @@
       <c r="F18" s="9" t="s">
         <v>971</v>
       </c>
-      <c r="G18" s="34"/>
-      <c r="H18" s="36"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="37"/>
       <c r="I18" s="9">
         <v>1</v>
       </c>
@@ -20883,8 +20883,8 @@
       <c r="F19" s="7" t="s">
         <v>967</v>
       </c>
-      <c r="G19" s="34"/>
-      <c r="H19" s="36"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="37"/>
       <c r="I19" s="7">
         <v>1</v>
       </c>
@@ -20947,8 +20947,8 @@
       <c r="F20" s="9" t="s">
         <v>963</v>
       </c>
-      <c r="G20" s="34"/>
-      <c r="H20" s="36"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="37"/>
       <c r="I20" s="9">
         <v>1</v>
       </c>
@@ -21011,8 +21011,8 @@
       <c r="F21" s="7" t="s">
         <v>959</v>
       </c>
-      <c r="G21" s="34"/>
-      <c r="H21" s="36"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="37"/>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -21067,8 +21067,8 @@
       <c r="F22" s="9" t="s">
         <v>955</v>
       </c>
-      <c r="G22" s="34"/>
-      <c r="H22" s="36"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="37"/>
       <c r="I22" s="9">
         <v>1</v>
       </c>
@@ -21131,8 +21131,8 @@
       <c r="F23" s="7" t="s">
         <v>951</v>
       </c>
-      <c r="G23" s="34"/>
-      <c r="H23" s="36"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="37"/>
       <c r="I23" s="7">
         <v>1</v>
       </c>
@@ -21195,8 +21195,8 @@
       <c r="F24" s="9" t="s">
         <v>947</v>
       </c>
-      <c r="G24" s="34"/>
-      <c r="H24" s="36"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="37"/>
       <c r="I24" s="9">
         <v>1</v>
       </c>
@@ -21259,8 +21259,8 @@
       <c r="F25" s="7" t="s">
         <v>943</v>
       </c>
-      <c r="G25" s="37"/>
-      <c r="H25" s="39"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="40"/>
       <c r="I25" s="7">
         <v>1</v>
       </c>
@@ -21475,18 +21475,18 @@
       <c r="F3" s="7" t="s">
         <v>802</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="33"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="34"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="33"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="34"/>
       <c r="L3" s="7">
         <v>1</v>
       </c>
-      <c r="M3" s="46"/>
+      <c r="M3" s="47"/>
       <c r="N3" s="7"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="33"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="34"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
@@ -21542,18 +21542,18 @@
       <c r="F4" s="9" t="s">
         <v>798</v>
       </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="36"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="37"/>
       <c r="I4" s="9"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="36"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="37"/>
       <c r="L4" s="9">
         <v>1</v>
       </c>
-      <c r="M4" s="47"/>
+      <c r="M4" s="48"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="36"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="37"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
@@ -21609,18 +21609,18 @@
       <c r="F5" s="7" t="s">
         <v>794</v>
       </c>
-      <c r="G5" s="34"/>
-      <c r="H5" s="36"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="37"/>
       <c r="I5" s="7"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="36"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="37"/>
       <c r="L5" s="7">
         <v>1</v>
       </c>
-      <c r="M5" s="47"/>
+      <c r="M5" s="48"/>
       <c r="N5" s="7"/>
-      <c r="O5" s="34"/>
-      <c r="P5" s="36"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="37"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -21676,16 +21676,16 @@
       <c r="F6" s="9" t="s">
         <v>790</v>
       </c>
-      <c r="G6" s="34"/>
-      <c r="H6" s="36"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="37"/>
       <c r="I6" s="9"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="36"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="37"/>
       <c r="L6" s="9"/>
-      <c r="M6" s="47"/>
+      <c r="M6" s="48"/>
       <c r="N6" s="9"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="36"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="37"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
@@ -21741,18 +21741,18 @@
       <c r="F7" s="7" t="s">
         <v>786</v>
       </c>
-      <c r="G7" s="34"/>
-      <c r="H7" s="36"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="37"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="36"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="37"/>
       <c r="L7" s="7">
         <v>1</v>
       </c>
-      <c r="M7" s="47"/>
+      <c r="M7" s="48"/>
       <c r="N7" s="7"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="36"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="37"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
@@ -21808,18 +21808,18 @@
       <c r="F8" s="9" t="s">
         <v>782</v>
       </c>
-      <c r="G8" s="34"/>
-      <c r="H8" s="36"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="37"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="36"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="37"/>
       <c r="L8" s="9">
         <v>1</v>
       </c>
-      <c r="M8" s="47"/>
+      <c r="M8" s="48"/>
       <c r="N8" s="9"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="36"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="37"/>
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
@@ -21875,18 +21875,18 @@
       <c r="F9" s="7" t="s">
         <v>778</v>
       </c>
-      <c r="G9" s="34"/>
-      <c r="H9" s="36"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="37"/>
       <c r="I9" s="7"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="36"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="37"/>
       <c r="L9" s="7">
         <v>1</v>
       </c>
-      <c r="M9" s="47"/>
+      <c r="M9" s="48"/>
       <c r="N9" s="7"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="36"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="37"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
@@ -21942,18 +21942,18 @@
       <c r="F10" s="9" t="s">
         <v>774</v>
       </c>
-      <c r="G10" s="34"/>
-      <c r="H10" s="36"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="37"/>
       <c r="I10" s="9"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="36"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="37"/>
       <c r="L10" s="9">
         <v>1</v>
       </c>
-      <c r="M10" s="47"/>
+      <c r="M10" s="48"/>
       <c r="N10" s="9"/>
-      <c r="O10" s="34"/>
-      <c r="P10" s="36"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="37"/>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
       <c r="S10" s="9"/>
@@ -22009,18 +22009,18 @@
       <c r="F11" s="7" t="s">
         <v>770</v>
       </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="36"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="37"/>
       <c r="I11" s="7"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="36"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="37"/>
       <c r="L11" s="7">
         <v>1</v>
       </c>
-      <c r="M11" s="47"/>
+      <c r="M11" s="48"/>
       <c r="N11" s="7"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="36"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="37"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
@@ -22076,18 +22076,18 @@
       <c r="F12" s="9" t="s">
         <v>766</v>
       </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="36"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="9"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="36"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="37"/>
       <c r="L12" s="9">
         <v>1</v>
       </c>
-      <c r="M12" s="47"/>
+      <c r="M12" s="48"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="36"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="37"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
@@ -22143,16 +22143,16 @@
       <c r="F13" s="7" t="s">
         <v>762</v>
       </c>
-      <c r="G13" s="34"/>
-      <c r="H13" s="36"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="7"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="36"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="37"/>
       <c r="L13" s="7"/>
-      <c r="M13" s="47"/>
+      <c r="M13" s="48"/>
       <c r="N13" s="7"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="36"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="37"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
@@ -22208,18 +22208,18 @@
       <c r="F14" s="9" t="s">
         <v>758</v>
       </c>
-      <c r="G14" s="34"/>
-      <c r="H14" s="36"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="37"/>
       <c r="I14" s="9"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="36"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="37"/>
       <c r="L14" s="9">
         <v>1</v>
       </c>
-      <c r="M14" s="47"/>
+      <c r="M14" s="48"/>
       <c r="N14" s="9"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="36"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="37"/>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
@@ -22275,16 +22275,16 @@
       <c r="F15" s="7" t="s">
         <v>754</v>
       </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="36"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="37"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="36"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="37"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="47"/>
+      <c r="M15" s="48"/>
       <c r="N15" s="7"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="36"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="37"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
@@ -22340,18 +22340,18 @@
       <c r="F16" s="9" t="s">
         <v>750</v>
       </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="36"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="37"/>
       <c r="I16" s="9"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="36"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="37"/>
       <c r="L16" s="9">
         <v>1</v>
       </c>
-      <c r="M16" s="47"/>
+      <c r="M16" s="48"/>
       <c r="N16" s="9"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="36"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="37"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
@@ -22407,18 +22407,18 @@
       <c r="F17" s="7" t="s">
         <v>746</v>
       </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="36"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="37"/>
       <c r="I17" s="7"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="36"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="37"/>
       <c r="L17" s="7">
         <v>1</v>
       </c>
-      <c r="M17" s="47"/>
+      <c r="M17" s="48"/>
       <c r="N17" s="7"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="36"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="37"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
@@ -22474,18 +22474,18 @@
       <c r="F18" s="9" t="s">
         <v>742</v>
       </c>
-      <c r="G18" s="34"/>
-      <c r="H18" s="36"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="37"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="36"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="37"/>
       <c r="L18" s="9">
         <v>1</v>
       </c>
-      <c r="M18" s="47"/>
+      <c r="M18" s="48"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="36"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="37"/>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
@@ -22541,18 +22541,18 @@
       <c r="F19" s="7" t="s">
         <v>738</v>
       </c>
-      <c r="G19" s="34"/>
-      <c r="H19" s="36"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="37"/>
       <c r="I19" s="7"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="36"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="37"/>
       <c r="L19" s="7">
         <v>1</v>
       </c>
-      <c r="M19" s="47"/>
+      <c r="M19" s="48"/>
       <c r="N19" s="7"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="36"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="37"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
@@ -22608,18 +22608,18 @@
       <c r="F20" s="9" t="s">
         <v>734</v>
       </c>
-      <c r="G20" s="34"/>
-      <c r="H20" s="36"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="37"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="36"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="37"/>
       <c r="L20" s="9">
         <v>1</v>
       </c>
-      <c r="M20" s="47"/>
+      <c r="M20" s="48"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="36"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="37"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
       <c r="S20" s="9"/>
@@ -22675,16 +22675,16 @@
       <c r="F21" s="7" t="s">
         <v>730</v>
       </c>
-      <c r="G21" s="34"/>
-      <c r="H21" s="36"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="37"/>
       <c r="I21" s="7"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="36"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="37"/>
       <c r="L21" s="7"/>
-      <c r="M21" s="47"/>
+      <c r="M21" s="48"/>
       <c r="N21" s="7"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="36"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="37"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
@@ -22740,16 +22740,16 @@
       <c r="F22" s="9" t="s">
         <v>726</v>
       </c>
-      <c r="G22" s="34"/>
-      <c r="H22" s="36"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="37"/>
       <c r="I22" s="9"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="36"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="37"/>
       <c r="L22" s="9"/>
-      <c r="M22" s="47"/>
+      <c r="M22" s="48"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="34"/>
-      <c r="P22" s="36"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="37"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
       <c r="S22" s="9"/>
@@ -22805,18 +22805,18 @@
       <c r="F23" s="7" t="s">
         <v>722</v>
       </c>
-      <c r="G23" s="34"/>
-      <c r="H23" s="36"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="37"/>
       <c r="I23" s="7"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="36"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="37"/>
       <c r="L23" s="7">
         <v>1</v>
       </c>
-      <c r="M23" s="47"/>
+      <c r="M23" s="48"/>
       <c r="N23" s="7"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="36"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="37"/>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
@@ -22872,18 +22872,18 @@
       <c r="F24" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="G24" s="34"/>
-      <c r="H24" s="36"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="37"/>
       <c r="I24" s="9"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="36"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="37"/>
       <c r="L24" s="9">
         <v>1</v>
       </c>
-      <c r="M24" s="47"/>
+      <c r="M24" s="48"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="36"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="37"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
       <c r="S24" s="9"/>
@@ -22939,18 +22939,18 @@
       <c r="F25" s="7" t="s">
         <v>714</v>
       </c>
-      <c r="G25" s="34"/>
-      <c r="H25" s="36"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="37"/>
       <c r="I25" s="7"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="36"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="37"/>
       <c r="L25" s="7">
         <v>1</v>
       </c>
-      <c r="M25" s="47"/>
+      <c r="M25" s="48"/>
       <c r="N25" s="7"/>
-      <c r="O25" s="34"/>
-      <c r="P25" s="36"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="37"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
@@ -23006,16 +23006,16 @@
       <c r="F26" s="9" t="s">
         <v>710</v>
       </c>
-      <c r="G26" s="34"/>
-      <c r="H26" s="36"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="37"/>
       <c r="I26" s="9"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="36"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="37"/>
       <c r="L26" s="9"/>
-      <c r="M26" s="47"/>
+      <c r="M26" s="48"/>
       <c r="N26" s="9"/>
-      <c r="O26" s="34"/>
-      <c r="P26" s="36"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="37"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
       <c r="S26" s="9"/>
@@ -23071,18 +23071,18 @@
       <c r="F27" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="G27" s="34"/>
-      <c r="H27" s="36"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="37"/>
       <c r="I27" s="7"/>
-      <c r="J27" s="34"/>
-      <c r="K27" s="36"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="37"/>
       <c r="L27" s="7">
         <v>1</v>
       </c>
-      <c r="M27" s="47"/>
+      <c r="M27" s="48"/>
       <c r="N27" s="7"/>
-      <c r="O27" s="34"/>
-      <c r="P27" s="36"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="37"/>
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
@@ -23138,18 +23138,18 @@
       <c r="F28" s="9" t="s">
         <v>702</v>
       </c>
-      <c r="G28" s="34"/>
-      <c r="H28" s="36"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="37"/>
       <c r="I28" s="9"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="36"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="37"/>
       <c r="L28" s="9">
         <v>1</v>
       </c>
-      <c r="M28" s="47"/>
+      <c r="M28" s="48"/>
       <c r="N28" s="9"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="36"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="37"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
       <c r="S28" s="9"/>
@@ -23205,18 +23205,18 @@
       <c r="F29" s="7" t="s">
         <v>698</v>
       </c>
-      <c r="G29" s="34"/>
-      <c r="H29" s="36"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="37"/>
       <c r="I29" s="7"/>
-      <c r="J29" s="34"/>
-      <c r="K29" s="36"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="37"/>
       <c r="L29" s="7">
         <v>1</v>
       </c>
-      <c r="M29" s="47"/>
+      <c r="M29" s="48"/>
       <c r="N29" s="7"/>
-      <c r="O29" s="34"/>
-      <c r="P29" s="36"/>
+      <c r="O29" s="35"/>
+      <c r="P29" s="37"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
@@ -23272,16 +23272,16 @@
       <c r="F30" s="9" t="s">
         <v>694</v>
       </c>
-      <c r="G30" s="34"/>
-      <c r="H30" s="36"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="37"/>
       <c r="I30" s="9"/>
-      <c r="J30" s="34"/>
-      <c r="K30" s="36"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="37"/>
       <c r="L30" s="9"/>
-      <c r="M30" s="47"/>
+      <c r="M30" s="48"/>
       <c r="N30" s="9"/>
-      <c r="O30" s="34"/>
-      <c r="P30" s="36"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="37"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
       <c r="S30" s="9"/>
@@ -23337,18 +23337,18 @@
       <c r="F31" s="7" t="s">
         <v>690</v>
       </c>
-      <c r="G31" s="34"/>
-      <c r="H31" s="36"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="37"/>
       <c r="I31" s="7"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="36"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="37"/>
       <c r="L31" s="7">
         <v>1</v>
       </c>
-      <c r="M31" s="47"/>
+      <c r="M31" s="48"/>
       <c r="N31" s="7"/>
-      <c r="O31" s="34"/>
-      <c r="P31" s="36"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="37"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
       <c r="S31" s="7"/>
@@ -23404,18 +23404,18 @@
       <c r="F32" s="9" t="s">
         <v>686</v>
       </c>
-      <c r="G32" s="34"/>
-      <c r="H32" s="36"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="37"/>
       <c r="I32" s="9"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="36"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="37"/>
       <c r="L32" s="9">
         <v>1</v>
       </c>
-      <c r="M32" s="47"/>
+      <c r="M32" s="48"/>
       <c r="N32" s="9"/>
-      <c r="O32" s="34"/>
-      <c r="P32" s="36"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="37"/>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
       <c r="S32" s="9"/>
@@ -23471,18 +23471,18 @@
       <c r="F33" s="7" t="s">
         <v>682</v>
       </c>
-      <c r="G33" s="34"/>
-      <c r="H33" s="36"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="37"/>
       <c r="I33" s="7"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="36"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="37"/>
       <c r="L33" s="7">
         <v>1</v>
       </c>
-      <c r="M33" s="47"/>
+      <c r="M33" s="48"/>
       <c r="N33" s="7"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="36"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="37"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
       <c r="S33" s="7"/>
@@ -23538,18 +23538,18 @@
       <c r="F34" s="9" t="s">
         <v>678</v>
       </c>
-      <c r="G34" s="34"/>
-      <c r="H34" s="36"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="37"/>
       <c r="I34" s="9"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="36"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="37"/>
       <c r="L34" s="9">
         <v>1</v>
       </c>
-      <c r="M34" s="47"/>
+      <c r="M34" s="48"/>
       <c r="N34" s="9"/>
-      <c r="O34" s="34"/>
-      <c r="P34" s="36"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="37"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
       <c r="S34" s="9"/>
@@ -23605,18 +23605,18 @@
       <c r="F35" s="7" t="s">
         <v>674</v>
       </c>
-      <c r="G35" s="34"/>
-      <c r="H35" s="36"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="37"/>
       <c r="I35" s="7"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="36"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="37"/>
       <c r="L35" s="7">
         <v>1</v>
       </c>
-      <c r="M35" s="47"/>
+      <c r="M35" s="48"/>
       <c r="N35" s="7"/>
-      <c r="O35" s="34"/>
-      <c r="P35" s="36"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="37"/>
       <c r="Q35" s="7"/>
       <c r="R35" s="7"/>
       <c r="S35" s="7"/>
@@ -23672,18 +23672,18 @@
       <c r="F36" s="9" t="s">
         <v>670</v>
       </c>
-      <c r="G36" s="34"/>
-      <c r="H36" s="36"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="37"/>
       <c r="I36" s="9"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="36"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="37"/>
       <c r="L36" s="9">
         <v>1</v>
       </c>
-      <c r="M36" s="47"/>
+      <c r="M36" s="48"/>
       <c r="N36" s="9"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="36"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="37"/>
       <c r="Q36" s="9"/>
       <c r="R36" s="9"/>
       <c r="S36" s="9"/>
@@ -23739,18 +23739,18 @@
       <c r="F37" s="7" t="s">
         <v>666</v>
       </c>
-      <c r="G37" s="34"/>
-      <c r="H37" s="36"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="37"/>
       <c r="I37" s="7"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="36"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="37"/>
       <c r="L37" s="7">
         <v>1</v>
       </c>
-      <c r="M37" s="47"/>
+      <c r="M37" s="48"/>
       <c r="N37" s="7"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="36"/>
+      <c r="O37" s="35"/>
+      <c r="P37" s="37"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="7"/>
       <c r="S37" s="7"/>
@@ -23806,18 +23806,18 @@
       <c r="F38" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="G38" s="34"/>
-      <c r="H38" s="36"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="37"/>
       <c r="I38" s="9"/>
-      <c r="J38" s="34"/>
-      <c r="K38" s="36"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="37"/>
       <c r="L38" s="9">
         <v>1</v>
       </c>
-      <c r="M38" s="47"/>
+      <c r="M38" s="48"/>
       <c r="N38" s="9"/>
-      <c r="O38" s="34"/>
-      <c r="P38" s="36"/>
+      <c r="O38" s="35"/>
+      <c r="P38" s="37"/>
       <c r="Q38" s="9"/>
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
@@ -23873,16 +23873,16 @@
       <c r="F39" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="G39" s="34"/>
-      <c r="H39" s="36"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="37"/>
       <c r="I39" s="7"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="36"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="37"/>
       <c r="L39" s="7"/>
-      <c r="M39" s="47"/>
+      <c r="M39" s="48"/>
       <c r="N39" s="7"/>
-      <c r="O39" s="34"/>
-      <c r="P39" s="36"/>
+      <c r="O39" s="35"/>
+      <c r="P39" s="37"/>
       <c r="Q39" s="7"/>
       <c r="R39" s="7"/>
       <c r="S39" s="7"/>
@@ -23938,18 +23938,18 @@
       <c r="F40" s="9" t="s">
         <v>654</v>
       </c>
-      <c r="G40" s="37"/>
-      <c r="H40" s="39"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="40"/>
       <c r="I40" s="9"/>
-      <c r="J40" s="37"/>
-      <c r="K40" s="39"/>
+      <c r="J40" s="38"/>
+      <c r="K40" s="40"/>
       <c r="L40" s="9">
         <v>1</v>
       </c>
-      <c r="M40" s="48"/>
+      <c r="M40" s="49"/>
       <c r="N40" s="9"/>
-      <c r="O40" s="37"/>
-      <c r="P40" s="39"/>
+      <c r="O40" s="38"/>
+      <c r="P40" s="40"/>
       <c r="Q40" s="9"/>
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
@@ -24135,17 +24135,17 @@
       <c r="D3" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="33"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="34"/>
       <c r="H3" s="7"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="33"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="34"/>
       <c r="K3" s="7"/>
-      <c r="L3" s="46"/>
+      <c r="L3" s="47"/>
       <c r="M3" s="7"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="33"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="34"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -24185,17 +24185,17 @@
       <c r="D4" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E4" s="34"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="36"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="37"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="36"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="37"/>
       <c r="K4" s="9"/>
-      <c r="L4" s="47"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="9"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="36"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="37"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
@@ -24235,17 +24235,17 @@
       <c r="D5" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="36"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="37"/>
       <c r="H5" s="7"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="36"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="37"/>
       <c r="K5" s="7"/>
-      <c r="L5" s="47"/>
+      <c r="L5" s="48"/>
       <c r="M5" s="7"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="36"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="37"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
@@ -24285,17 +24285,17 @@
       <c r="D6" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="36"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="37"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="36"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="37"/>
       <c r="K6" s="9"/>
-      <c r="L6" s="47"/>
+      <c r="L6" s="48"/>
       <c r="M6" s="9"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="36"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="37"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
@@ -24335,17 +24335,17 @@
       <c r="D7" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="36"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="37"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="36"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="37"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="47"/>
+      <c r="L7" s="48"/>
       <c r="M7" s="7"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="36"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="37"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
@@ -24385,17 +24385,17 @@
       <c r="D8" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E8" s="34"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="36"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="37"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="36"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="37"/>
       <c r="K8" s="9"/>
-      <c r="L8" s="47"/>
+      <c r="L8" s="48"/>
       <c r="M8" s="9"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="36"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="37"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
@@ -24435,17 +24435,17 @@
       <c r="D9" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E9" s="34"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="36"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="37"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="36"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="37"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="47"/>
+      <c r="L9" s="48"/>
       <c r="M9" s="7"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="36"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="37"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
@@ -24485,17 +24485,17 @@
       <c r="D10" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E10" s="34"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="36"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="37"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="36"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="37"/>
       <c r="K10" s="9"/>
-      <c r="L10" s="47"/>
+      <c r="L10" s="48"/>
       <c r="M10" s="9"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="36"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="37"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
@@ -24535,17 +24535,17 @@
       <c r="D11" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="36"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="7"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="36"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="37"/>
       <c r="K11" s="7"/>
-      <c r="L11" s="47"/>
+      <c r="L11" s="48"/>
       <c r="M11" s="7"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="36"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="37"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
@@ -24585,17 +24585,17 @@
       <c r="D12" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E12" s="34"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="36"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="37"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="36"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="37"/>
       <c r="K12" s="9"/>
-      <c r="L12" s="47"/>
+      <c r="L12" s="48"/>
       <c r="M12" s="9"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="36"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="37"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
@@ -24635,17 +24635,17 @@
       <c r="D13" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="36"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="37"/>
       <c r="H13" s="7"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="36"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="37"/>
       <c r="K13" s="7"/>
-      <c r="L13" s="47"/>
+      <c r="L13" s="48"/>
       <c r="M13" s="7"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="36"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="37"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -24685,17 +24685,17 @@
       <c r="D14" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E14" s="34"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="36"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="37"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="36"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="37"/>
       <c r="K14" s="9"/>
-      <c r="L14" s="47"/>
+      <c r="L14" s="48"/>
       <c r="M14" s="9"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="36"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="37"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
@@ -24735,17 +24735,17 @@
       <c r="D15" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E15" s="34"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="36"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="37"/>
       <c r="H15" s="7"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="36"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="37"/>
       <c r="K15" s="7"/>
-      <c r="L15" s="47"/>
+      <c r="L15" s="48"/>
       <c r="M15" s="7"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="36"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="37"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
@@ -24785,17 +24785,17 @@
       <c r="D16" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E16" s="34"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="36"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="37"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="36"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="37"/>
       <c r="K16" s="9"/>
-      <c r="L16" s="47"/>
+      <c r="L16" s="48"/>
       <c r="M16" s="9"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="36"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="37"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
@@ -24835,17 +24835,17 @@
       <c r="D17" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="36"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="37"/>
       <c r="H17" s="7"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="36"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="37"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="47"/>
+      <c r="L17" s="48"/>
       <c r="M17" s="7"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="36"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="37"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
@@ -24885,17 +24885,17 @@
       <c r="D18" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="36"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="37"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="36"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="37"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="47"/>
+      <c r="L18" s="48"/>
       <c r="M18" s="9"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="36"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="37"/>
       <c r="P18" s="9"/>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
@@ -24935,17 +24935,17 @@
       <c r="D19" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="36"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="37"/>
       <c r="H19" s="7"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="36"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="37"/>
       <c r="K19" s="7"/>
-      <c r="L19" s="47"/>
+      <c r="L19" s="48"/>
       <c r="M19" s="7"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="36"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="37"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
@@ -24985,17 +24985,17 @@
       <c r="D20" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="36"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="37"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="36"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="37"/>
       <c r="K20" s="9"/>
-      <c r="L20" s="47"/>
+      <c r="L20" s="48"/>
       <c r="M20" s="9"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="36"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="37"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
@@ -25035,17 +25035,17 @@
       <c r="D21" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E21" s="34"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="36"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="37"/>
       <c r="H21" s="7"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="36"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="37"/>
       <c r="K21" s="7"/>
-      <c r="L21" s="47"/>
+      <c r="L21" s="48"/>
       <c r="M21" s="7"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="36"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="37"/>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
@@ -25085,17 +25085,17 @@
       <c r="D22" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E22" s="34"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="36"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="37"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="36"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="37"/>
       <c r="K22" s="9"/>
-      <c r="L22" s="47"/>
+      <c r="L22" s="48"/>
       <c r="M22" s="9"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="36"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="37"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
@@ -25135,17 +25135,17 @@
       <c r="D23" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E23" s="34"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="36"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="37"/>
       <c r="H23" s="7"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="36"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="37"/>
       <c r="K23" s="7"/>
-      <c r="L23" s="47"/>
+      <c r="L23" s="48"/>
       <c r="M23" s="7"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="36"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="37"/>
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
@@ -25185,17 +25185,17 @@
       <c r="D24" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E24" s="34"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="36"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="37"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="36"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="37"/>
       <c r="K24" s="9"/>
-      <c r="L24" s="47"/>
+      <c r="L24" s="48"/>
       <c r="M24" s="9"/>
-      <c r="N24" s="34"/>
-      <c r="O24" s="36"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="37"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
@@ -25235,17 +25235,17 @@
       <c r="D25" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E25" s="34"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="36"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="37"/>
       <c r="H25" s="7"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="36"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="37"/>
       <c r="K25" s="7"/>
-      <c r="L25" s="47"/>
+      <c r="L25" s="48"/>
       <c r="M25" s="7"/>
-      <c r="N25" s="34"/>
-      <c r="O25" s="36"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="37"/>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
@@ -25285,17 +25285,17 @@
       <c r="D26" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E26" s="34"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="36"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="37"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="36"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="37"/>
       <c r="K26" s="9"/>
-      <c r="L26" s="47"/>
+      <c r="L26" s="48"/>
       <c r="M26" s="9"/>
-      <c r="N26" s="34"/>
-      <c r="O26" s="36"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="37"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
@@ -25335,17 +25335,17 @@
       <c r="D27" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E27" s="34"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="36"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="37"/>
       <c r="H27" s="7"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="36"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="37"/>
       <c r="K27" s="7"/>
-      <c r="L27" s="47"/>
+      <c r="L27" s="48"/>
       <c r="M27" s="7"/>
-      <c r="N27" s="34"/>
-      <c r="O27" s="36"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="37"/>
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
@@ -25385,17 +25385,17 @@
       <c r="D28" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E28" s="34"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="36"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="37"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="36"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="37"/>
       <c r="K28" s="9"/>
-      <c r="L28" s="47"/>
+      <c r="L28" s="48"/>
       <c r="M28" s="9"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="36"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="37"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
@@ -25435,17 +25435,17 @@
       <c r="D29" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E29" s="34"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="36"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="37"/>
       <c r="H29" s="7"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="36"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="37"/>
       <c r="K29" s="7"/>
-      <c r="L29" s="47"/>
+      <c r="L29" s="48"/>
       <c r="M29" s="7"/>
-      <c r="N29" s="34"/>
-      <c r="O29" s="36"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="37"/>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
@@ -25485,17 +25485,17 @@
       <c r="D30" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E30" s="34"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="36"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="37"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="36"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="37"/>
       <c r="K30" s="9"/>
-      <c r="L30" s="47"/>
+      <c r="L30" s="48"/>
       <c r="M30" s="9"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="36"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="37"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
@@ -25535,17 +25535,17 @@
       <c r="D31" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E31" s="34"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="36"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="37"/>
       <c r="H31" s="7"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="36"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="37"/>
       <c r="K31" s="7"/>
-      <c r="L31" s="47"/>
+      <c r="L31" s="48"/>
       <c r="M31" s="7"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="36"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="37"/>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
@@ -25585,17 +25585,17 @@
       <c r="D32" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E32" s="34"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="36"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="37"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="36"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="37"/>
       <c r="K32" s="9"/>
-      <c r="L32" s="47"/>
+      <c r="L32" s="48"/>
       <c r="M32" s="9"/>
-      <c r="N32" s="34"/>
-      <c r="O32" s="36"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="37"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
@@ -25635,17 +25635,17 @@
       <c r="D33" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E33" s="34"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="36"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="37"/>
       <c r="H33" s="7"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="36"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="37"/>
       <c r="K33" s="7"/>
-      <c r="L33" s="47"/>
+      <c r="L33" s="48"/>
       <c r="M33" s="7"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="36"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="37"/>
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
@@ -25685,17 +25685,17 @@
       <c r="D34" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E34" s="34"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="36"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="37"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="36"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="37"/>
       <c r="K34" s="9"/>
-      <c r="L34" s="47"/>
+      <c r="L34" s="48"/>
       <c r="M34" s="9"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="36"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="37"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
@@ -25735,17 +25735,17 @@
       <c r="D35" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E35" s="34"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="36"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="37"/>
       <c r="H35" s="7"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="36"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="37"/>
       <c r="K35" s="7"/>
-      <c r="L35" s="47"/>
+      <c r="L35" s="48"/>
       <c r="M35" s="7"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="36"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="37"/>
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
       <c r="R35" s="7"/>
@@ -25785,17 +25785,17 @@
       <c r="D36" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E36" s="34"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="36"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="37"/>
       <c r="H36" s="9"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="36"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="37"/>
       <c r="K36" s="9"/>
-      <c r="L36" s="47"/>
+      <c r="L36" s="48"/>
       <c r="M36" s="9"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="36"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="37"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="9"/>
       <c r="R36" s="9"/>
@@ -25835,17 +25835,17 @@
       <c r="D37" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E37" s="34"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="36"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="37"/>
       <c r="H37" s="7"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="36"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="37"/>
       <c r="K37" s="7"/>
-      <c r="L37" s="47"/>
+      <c r="L37" s="48"/>
       <c r="M37" s="7"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="36"/>
+      <c r="N37" s="35"/>
+      <c r="O37" s="37"/>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="7"/>
@@ -25885,17 +25885,17 @@
       <c r="D38" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E38" s="37"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="39"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="40"/>
       <c r="H38" s="9"/>
-      <c r="I38" s="37"/>
-      <c r="J38" s="39"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="40"/>
       <c r="K38" s="9"/>
-      <c r="L38" s="48"/>
+      <c r="L38" s="49"/>
       <c r="M38" s="9"/>
-      <c r="N38" s="37"/>
-      <c r="O38" s="39"/>
+      <c r="N38" s="38"/>
+      <c r="O38" s="40"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="9"/>
       <c r="R38" s="9"/>

--- a/Asistencias/Asistencias_General.xlsx
+++ b/Asistencias/Asistencias_General.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlosmartinez/Proyectos/Github/CalculoDiferencialTNM/Asistencias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFE2071-99EB-5247-BF03-B13F825ACF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A07102-CC5C-B948-8BD4-8CE5DB8847F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M13_CI" sheetId="7" r:id="rId1"/>
@@ -3931,7 +3931,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4007,6 +4007,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4061,15 +4062,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4538,9 +4530,9 @@
       <c r="F3" s="26" t="s">
         <v>939</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="37"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="38"/>
       <c r="J3" s="26"/>
       <c r="K3" s="26"/>
       <c r="L3" s="30">
@@ -4596,9 +4588,9 @@
       <c r="F4" s="26" t="s">
         <v>935</v>
       </c>
-      <c r="G4" s="38"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="40"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="41"/>
       <c r="J4" s="26">
         <v>1</v>
       </c>
@@ -4688,9 +4680,9 @@
       <c r="F5" s="7" t="s">
         <v>931</v>
       </c>
-      <c r="G5" s="38"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="40"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="41"/>
       <c r="J5" s="7">
         <v>1</v>
       </c>
@@ -4800,9 +4792,9 @@
       <c r="F6" s="9" t="s">
         <v>927</v>
       </c>
-      <c r="G6" s="38"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="40"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="41"/>
       <c r="J6" s="9"/>
       <c r="K6" s="9">
         <v>1</v>
@@ -4910,9 +4902,9 @@
       <c r="F7" s="7" t="s">
         <v>922</v>
       </c>
-      <c r="G7" s="38"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="40"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="41"/>
       <c r="J7" s="7">
         <v>1</v>
       </c>
@@ -5022,9 +5014,9 @@
       <c r="F8" s="9" t="s">
         <v>918</v>
       </c>
-      <c r="G8" s="38"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="40"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="9">
         <v>1</v>
       </c>
@@ -5132,9 +5124,9 @@
       <c r="F9" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="40"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="7">
         <v>1</v>
       </c>
@@ -5244,9 +5236,9 @@
       <c r="F10" s="9" t="s">
         <v>910</v>
       </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="40"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="41"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="13">
@@ -5352,9 +5344,9 @@
       <c r="F11" s="7" t="s">
         <v>906</v>
       </c>
-      <c r="G11" s="38"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="40"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="41"/>
       <c r="J11" s="7">
         <v>1</v>
       </c>
@@ -5464,9 +5456,9 @@
       <c r="F12" s="9" t="s">
         <v>902</v>
       </c>
-      <c r="G12" s="38"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="40"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="41"/>
       <c r="J12" s="9"/>
       <c r="K12" s="9">
         <v>1</v>
@@ -5568,9 +5560,9 @@
       <c r="F13" s="26" t="s">
         <v>898</v>
       </c>
-      <c r="G13" s="38"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="40"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="41"/>
       <c r="J13" s="26"/>
       <c r="K13" s="26"/>
       <c r="L13" s="30">
@@ -5626,9 +5618,9 @@
       <c r="F14" s="9" t="s">
         <v>894</v>
       </c>
-      <c r="G14" s="38"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="40"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="41"/>
       <c r="J14" s="9">
         <v>1</v>
       </c>
@@ -5738,9 +5730,9 @@
       <c r="F15" s="7" t="s">
         <v>890</v>
       </c>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="41"/>
       <c r="J15" s="7">
         <v>1</v>
       </c>
@@ -5850,9 +5842,9 @@
       <c r="F16" s="26" t="s">
         <v>886</v>
       </c>
-      <c r="G16" s="38"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="41"/>
       <c r="J16" s="26"/>
       <c r="K16" s="26"/>
       <c r="L16" s="30">
@@ -5908,9 +5900,9 @@
       <c r="F17" s="7" t="s">
         <v>882</v>
       </c>
-      <c r="G17" s="38"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="40"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="41"/>
       <c r="J17" s="7">
         <v>1</v>
       </c>
@@ -6018,9 +6010,9 @@
       <c r="F18" s="9" t="s">
         <v>878</v>
       </c>
-      <c r="G18" s="38"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="40"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="41"/>
       <c r="J18" s="9">
         <v>1</v>
       </c>
@@ -6130,9 +6122,9 @@
       <c r="F19" s="7" t="s">
         <v>874</v>
       </c>
-      <c r="G19" s="38"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="41"/>
       <c r="J19" s="7">
         <v>1</v>
       </c>
@@ -6242,9 +6234,9 @@
       <c r="F20" s="9" t="s">
         <v>870</v>
       </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="40"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
       <c r="J20" s="9">
         <v>1</v>
       </c>
@@ -6352,9 +6344,9 @@
       <c r="F21" s="7" t="s">
         <v>866</v>
       </c>
-      <c r="G21" s="38"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="41"/>
       <c r="J21" s="7">
         <v>1</v>
       </c>
@@ -6464,9 +6456,9 @@
       <c r="F22" s="9" t="s">
         <v>862</v>
       </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="41"/>
       <c r="J22" s="9">
         <v>1</v>
       </c>
@@ -6574,9 +6566,9 @@
       <c r="F23" s="7" t="s">
         <v>858</v>
       </c>
-      <c r="G23" s="38"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="41"/>
       <c r="J23" s="7">
         <v>1</v>
       </c>
@@ -6684,9 +6676,9 @@
       <c r="F24" s="9" t="s">
         <v>854</v>
       </c>
-      <c r="G24" s="38"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="41"/>
       <c r="J24" s="9">
         <v>1</v>
       </c>
@@ -6796,9 +6788,9 @@
       <c r="F25" s="26" t="s">
         <v>850</v>
       </c>
-      <c r="G25" s="38"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="41"/>
       <c r="J25" s="26">
         <v>1</v>
       </c>
@@ -6858,9 +6850,9 @@
       <c r="F26" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="41"/>
       <c r="J26" s="9">
         <v>1</v>
       </c>
@@ -6966,9 +6958,9 @@
       <c r="F27" s="7" t="s">
         <v>842</v>
       </c>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="41"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
       <c r="L27" s="12">
@@ -7074,9 +7066,9 @@
       <c r="F28" s="26" t="s">
         <v>838</v>
       </c>
-      <c r="G28" s="38"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="41"/>
       <c r="J28" s="26">
         <v>1</v>
       </c>
@@ -7160,9 +7152,9 @@
       <c r="F29" s="7" t="s">
         <v>834</v>
       </c>
-      <c r="G29" s="38"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="41"/>
       <c r="J29" s="7">
         <v>1</v>
       </c>
@@ -7270,9 +7262,9 @@
       <c r="F30" s="9" t="s">
         <v>830</v>
       </c>
-      <c r="G30" s="38"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="40"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="41"/>
       <c r="J30" s="9">
         <v>1</v>
       </c>
@@ -7382,9 +7374,9 @@
       <c r="F31" s="26" t="s">
         <v>826</v>
       </c>
-      <c r="G31" s="38"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="40"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="41"/>
       <c r="J31" s="26"/>
       <c r="K31" s="26">
         <v>1</v>
@@ -7453,131 +7445,131 @@
       <c r="AO31" s="26"/>
       <c r="AP31" s="26"/>
     </row>
-    <row r="32" spans="1:42" s="56" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="53" t="s">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A32" s="32" t="s">
         <v>825</v>
       </c>
-      <c r="B32" s="53">
-        <v>1</v>
-      </c>
-      <c r="C32" s="54" t="s">
+      <c r="B32" s="32">
+        <v>1</v>
+      </c>
+      <c r="C32" s="33" t="s">
         <v>824</v>
       </c>
-      <c r="D32" s="53" t="s">
+      <c r="D32" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="E32" s="55" t="s">
+      <c r="E32" s="34" t="s">
         <v>823</v>
       </c>
-      <c r="F32" s="53" t="s">
+      <c r="F32" s="32" t="s">
         <v>822</v>
       </c>
-      <c r="G32" s="38"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="53"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="53"/>
-      <c r="M32" s="53"/>
-      <c r="N32" s="53"/>
-      <c r="O32" s="53"/>
-      <c r="P32" s="53"/>
-      <c r="Q32" s="53"/>
-      <c r="R32" s="53"/>
-      <c r="S32" s="53"/>
-      <c r="T32" s="53"/>
-      <c r="U32" s="53"/>
-      <c r="V32" s="53"/>
-      <c r="W32" s="53">
-        <v>1</v>
-      </c>
-      <c r="X32" s="53">
-        <v>1</v>
-      </c>
-      <c r="Y32" s="53">
-        <v>1</v>
-      </c>
-      <c r="Z32" s="53">
-        <v>1</v>
-      </c>
-      <c r="AA32" s="53"/>
-      <c r="AB32" s="53"/>
-      <c r="AC32" s="53"/>
-      <c r="AD32" s="53"/>
-      <c r="AE32" s="53"/>
-      <c r="AF32" s="53"/>
-      <c r="AG32" s="53"/>
-      <c r="AH32" s="53"/>
-      <c r="AI32" s="53"/>
-      <c r="AJ32" s="53"/>
-      <c r="AK32" s="53">
-        <v>1</v>
-      </c>
-      <c r="AL32" s="53"/>
-      <c r="AM32" s="53"/>
-      <c r="AN32" s="53"/>
-      <c r="AO32" s="53"/>
-      <c r="AP32" s="53"/>
-    </row>
-    <row r="33" spans="1:42" s="56" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="53" t="s">
+      <c r="G32" s="39"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="32">
+        <v>1</v>
+      </c>
+      <c r="X32" s="32">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="32">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="32">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="32"/>
+      <c r="AB32" s="32"/>
+      <c r="AC32" s="32"/>
+      <c r="AD32" s="32"/>
+      <c r="AE32" s="32"/>
+      <c r="AF32" s="32"/>
+      <c r="AG32" s="32"/>
+      <c r="AH32" s="32"/>
+      <c r="AI32" s="32"/>
+      <c r="AJ32" s="32"/>
+      <c r="AK32" s="32">
+        <v>1</v>
+      </c>
+      <c r="AL32" s="32"/>
+      <c r="AM32" s="32"/>
+      <c r="AN32" s="32"/>
+      <c r="AO32" s="32"/>
+      <c r="AP32" s="32"/>
+    </row>
+    <row r="33" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A33" s="32" t="s">
         <v>821</v>
       </c>
-      <c r="B33" s="53">
-        <v>1</v>
-      </c>
-      <c r="C33" s="54" t="s">
+      <c r="B33" s="32">
+        <v>1</v>
+      </c>
+      <c r="C33" s="33" t="s">
         <v>820</v>
       </c>
-      <c r="D33" s="53" t="s">
+      <c r="D33" s="32" t="s">
         <v>317</v>
       </c>
-      <c r="E33" s="55" t="s">
+      <c r="E33" s="34" t="s">
         <v>819</v>
       </c>
-      <c r="F33" s="53" t="s">
+      <c r="F33" s="32" t="s">
         <v>818</v>
       </c>
-      <c r="G33" s="38"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="57">
-        <v>1</v>
-      </c>
-      <c r="M33" s="53"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="53"/>
-      <c r="P33" s="53"/>
-      <c r="Q33" s="53"/>
-      <c r="R33" s="53"/>
-      <c r="S33" s="53"/>
-      <c r="T33" s="53"/>
-      <c r="U33" s="53"/>
-      <c r="V33" s="53"/>
-      <c r="W33" s="53"/>
-      <c r="X33" s="53"/>
-      <c r="Y33" s="53"/>
-      <c r="Z33" s="53"/>
-      <c r="AA33" s="53"/>
-      <c r="AB33" s="53"/>
-      <c r="AC33" s="53"/>
-      <c r="AD33" s="53"/>
-      <c r="AE33" s="53"/>
-      <c r="AF33" s="53"/>
-      <c r="AG33" s="53"/>
-      <c r="AH33" s="53"/>
-      <c r="AI33" s="53"/>
-      <c r="AJ33" s="53"/>
-      <c r="AK33" s="53">
-        <v>1</v>
-      </c>
-      <c r="AL33" s="53"/>
-      <c r="AM33" s="53"/>
-      <c r="AN33" s="53"/>
-      <c r="AO33" s="53"/>
-      <c r="AP33" s="53"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="35">
+        <v>1</v>
+      </c>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="32"/>
+      <c r="U33" s="32"/>
+      <c r="V33" s="32"/>
+      <c r="W33" s="32"/>
+      <c r="X33" s="32"/>
+      <c r="Y33" s="32"/>
+      <c r="Z33" s="32"/>
+      <c r="AA33" s="32"/>
+      <c r="AB33" s="32"/>
+      <c r="AC33" s="32"/>
+      <c r="AD33" s="32"/>
+      <c r="AE33" s="32"/>
+      <c r="AF33" s="32"/>
+      <c r="AG33" s="32"/>
+      <c r="AH33" s="32"/>
+      <c r="AI33" s="32"/>
+      <c r="AJ33" s="32"/>
+      <c r="AK33" s="32">
+        <v>1</v>
+      </c>
+      <c r="AL33" s="32"/>
+      <c r="AM33" s="32"/>
+      <c r="AN33" s="32"/>
+      <c r="AO33" s="32"/>
+      <c r="AP33" s="32"/>
     </row>
     <row r="34" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
@@ -7598,9 +7590,9 @@
       <c r="F34" s="9" t="s">
         <v>814</v>
       </c>
-      <c r="G34" s="38"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="40"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="41"/>
       <c r="J34" s="9">
         <v>1</v>
       </c>
@@ -7675,83 +7667,83 @@
       <c r="AO34" s="9"/>
       <c r="AP34" s="9"/>
     </row>
-    <row r="35" spans="1:42" s="56" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="53" t="s">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A35" s="32" t="s">
         <v>813</v>
       </c>
-      <c r="B35" s="53" t="s">
+      <c r="B35" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="54" t="s">
+      <c r="C35" s="33" t="s">
         <v>812</v>
       </c>
-      <c r="D35" s="53" t="s">
+      <c r="D35" s="32" t="s">
         <v>317</v>
       </c>
-      <c r="E35" s="55" t="s">
+      <c r="E35" s="34" t="s">
         <v>811</v>
       </c>
-      <c r="F35" s="53" t="s">
+      <c r="F35" s="32" t="s">
         <v>810</v>
       </c>
-      <c r="G35" s="38"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="53">
-        <v>1</v>
-      </c>
-      <c r="L35" s="53"/>
-      <c r="M35" s="53">
-        <v>1</v>
-      </c>
-      <c r="N35" s="53">
-        <v>1</v>
-      </c>
-      <c r="O35" s="53">
-        <v>1</v>
-      </c>
-      <c r="P35" s="53">
-        <v>1</v>
-      </c>
-      <c r="Q35" s="53">
-        <v>1</v>
-      </c>
-      <c r="R35" s="53">
-        <v>1</v>
-      </c>
-      <c r="S35" s="53">
-        <v>1</v>
-      </c>
-      <c r="T35" s="53"/>
-      <c r="U35" s="53">
-        <v>1</v>
-      </c>
-      <c r="V35" s="53">
-        <v>1</v>
-      </c>
-      <c r="W35" s="53"/>
-      <c r="X35" s="53"/>
-      <c r="Y35" s="53"/>
-      <c r="Z35" s="53"/>
-      <c r="AA35" s="53"/>
-      <c r="AB35" s="53"/>
-      <c r="AC35" s="53"/>
-      <c r="AD35" s="53"/>
-      <c r="AE35" s="53"/>
-      <c r="AF35" s="53"/>
-      <c r="AG35" s="53"/>
-      <c r="AH35" s="53"/>
-      <c r="AI35" s="53"/>
-      <c r="AJ35" s="53"/>
-      <c r="AK35" s="53">
-        <v>1</v>
-      </c>
-      <c r="AL35" s="53"/>
-      <c r="AM35" s="53"/>
-      <c r="AN35" s="53"/>
-      <c r="AO35" s="53"/>
-      <c r="AP35" s="53"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32">
+        <v>1</v>
+      </c>
+      <c r="L35" s="32"/>
+      <c r="M35" s="32">
+        <v>1</v>
+      </c>
+      <c r="N35" s="32">
+        <v>1</v>
+      </c>
+      <c r="O35" s="32">
+        <v>1</v>
+      </c>
+      <c r="P35" s="32">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="32">
+        <v>1</v>
+      </c>
+      <c r="R35" s="32">
+        <v>1</v>
+      </c>
+      <c r="S35" s="32">
+        <v>1</v>
+      </c>
+      <c r="T35" s="32"/>
+      <c r="U35" s="32">
+        <v>1</v>
+      </c>
+      <c r="V35" s="32">
+        <v>1</v>
+      </c>
+      <c r="W35" s="32"/>
+      <c r="X35" s="32"/>
+      <c r="Y35" s="32"/>
+      <c r="Z35" s="32"/>
+      <c r="AA35" s="32"/>
+      <c r="AB35" s="32"/>
+      <c r="AC35" s="32"/>
+      <c r="AD35" s="32"/>
+      <c r="AE35" s="32"/>
+      <c r="AF35" s="32"/>
+      <c r="AG35" s="32"/>
+      <c r="AH35" s="32"/>
+      <c r="AI35" s="32"/>
+      <c r="AJ35" s="32"/>
+      <c r="AK35" s="32">
+        <v>1</v>
+      </c>
+      <c r="AL35" s="32"/>
+      <c r="AM35" s="32"/>
+      <c r="AN35" s="32"/>
+      <c r="AO35" s="32"/>
+      <c r="AP35" s="32"/>
     </row>
     <row r="36" spans="1:42" s="29" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="26" t="s">
@@ -7772,9 +7764,9 @@
       <c r="F36" s="26" t="s">
         <v>806</v>
       </c>
-      <c r="G36" s="41"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="43"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="44"/>
       <c r="J36" s="26">
         <v>1</v>
       </c>
@@ -7984,22 +7976,22 @@
         <v>2</v>
       </c>
       <c r="AK2" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL2" s="11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM2" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN2" s="11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO2" s="11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AP2" s="11">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.2">
@@ -8021,8 +8013,8 @@
       <c r="F3" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="37"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="38"/>
       <c r="I3" s="7">
         <v>1</v>
       </c>
@@ -8107,7 +8099,9 @@
       <c r="AJ3" s="7">
         <v>1</v>
       </c>
-      <c r="AK3" s="7"/>
+      <c r="AK3" s="7">
+        <v>1</v>
+      </c>
       <c r="AL3" s="7"/>
       <c r="AM3" s="7"/>
       <c r="AN3" s="7"/>
@@ -8133,8 +8127,8 @@
       <c r="F4" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="G4" s="38"/>
-      <c r="H4" s="40"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="41"/>
       <c r="I4" s="9">
         <v>1</v>
       </c>
@@ -8213,7 +8207,9 @@
         <v>1</v>
       </c>
       <c r="AJ4" s="9"/>
-      <c r="AK4" s="9"/>
+      <c r="AK4" s="9">
+        <v>1</v>
+      </c>
       <c r="AL4" s="9"/>
       <c r="AM4" s="9"/>
       <c r="AN4" s="9"/>
@@ -8239,8 +8235,8 @@
       <c r="F5" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="G5" s="38"/>
-      <c r="H5" s="40"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="41"/>
       <c r="I5" s="7">
         <v>1</v>
       </c>
@@ -8317,7 +8313,9 @@
         <v>1</v>
       </c>
       <c r="AJ5" s="7"/>
-      <c r="AK5" s="7"/>
+      <c r="AK5" s="7">
+        <v>1</v>
+      </c>
       <c r="AL5" s="7"/>
       <c r="AM5" s="7"/>
       <c r="AN5" s="7"/>
@@ -8343,8 +8341,8 @@
       <c r="F6" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="G6" s="38"/>
-      <c r="H6" s="40"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="41"/>
       <c r="I6" s="9">
         <v>1</v>
       </c>
@@ -8437,8 +8435,8 @@
       <c r="F7" s="26" t="s">
         <v>412</v>
       </c>
-      <c r="G7" s="38"/>
-      <c r="H7" s="40"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="41"/>
       <c r="I7" s="26"/>
       <c r="J7" s="26"/>
       <c r="K7" s="26"/>
@@ -8493,8 +8491,8 @@
       <c r="F8" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="G8" s="38"/>
-      <c r="H8" s="40"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="41"/>
       <c r="I8" s="9">
         <v>1</v>
       </c>
@@ -8581,8 +8579,8 @@
       <c r="F9" s="26" t="s">
         <v>404</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="40"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="41"/>
       <c r="I9" s="26"/>
       <c r="J9" s="26"/>
       <c r="K9" s="26"/>
@@ -8637,8 +8635,8 @@
       <c r="F10" s="26" t="s">
         <v>400</v>
       </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="40"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="41"/>
       <c r="I10" s="26"/>
       <c r="J10" s="26"/>
       <c r="K10" s="26">
@@ -8697,8 +8695,8 @@
       <c r="F11" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="G11" s="38"/>
-      <c r="H11" s="40"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="41"/>
       <c r="I11" s="7">
         <v>1</v>
       </c>
@@ -8781,7 +8779,9 @@
       <c r="AJ11" s="7">
         <v>1</v>
       </c>
-      <c r="AK11" s="7"/>
+      <c r="AK11" s="7">
+        <v>1</v>
+      </c>
       <c r="AL11" s="7"/>
       <c r="AM11" s="7"/>
       <c r="AN11" s="7"/>
@@ -8807,8 +8807,8 @@
       <c r="F12" s="26" t="s">
         <v>392</v>
       </c>
-      <c r="G12" s="38"/>
-      <c r="H12" s="40"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="41"/>
       <c r="I12" s="26"/>
       <c r="J12" s="26"/>
       <c r="K12" s="26"/>
@@ -8865,8 +8865,8 @@
       <c r="F13" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="G13" s="38"/>
-      <c r="H13" s="40"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="41"/>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
@@ -8923,8 +8923,8 @@
       <c r="F14" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="G14" s="38"/>
-      <c r="H14" s="40"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="41"/>
       <c r="I14" s="9">
         <v>1</v>
       </c>
@@ -9009,7 +9009,9 @@
       <c r="AJ14" s="9">
         <v>1</v>
       </c>
-      <c r="AK14" s="9"/>
+      <c r="AK14" s="9">
+        <v>1</v>
+      </c>
       <c r="AL14" s="9"/>
       <c r="AM14" s="9"/>
       <c r="AN14" s="9"/>
@@ -9035,8 +9037,8 @@
       <c r="F15" s="26" t="s">
         <v>380</v>
       </c>
-      <c r="G15" s="38"/>
-      <c r="H15" s="40"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="41"/>
       <c r="I15" s="26"/>
       <c r="J15" s="26"/>
       <c r="K15" s="26"/>
@@ -9091,8 +9093,8 @@
       <c r="F16" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="G16" s="38"/>
-      <c r="H16" s="40"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="41"/>
       <c r="I16" s="9">
         <v>1</v>
       </c>
@@ -9167,7 +9169,9 @@
       <c r="AJ16" s="9">
         <v>1</v>
       </c>
-      <c r="AK16" s="9"/>
+      <c r="AK16" s="9">
+        <v>1</v>
+      </c>
       <c r="AL16" s="9"/>
       <c r="AM16" s="9"/>
       <c r="AN16" s="9"/>
@@ -9193,8 +9197,8 @@
       <c r="F17" s="32" t="s">
         <v>371</v>
       </c>
-      <c r="G17" s="38"/>
-      <c r="H17" s="40"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="41"/>
       <c r="I17" s="32">
         <v>1</v>
       </c>
@@ -9275,7 +9279,9 @@
       <c r="AJ17" s="32">
         <v>1</v>
       </c>
-      <c r="AK17" s="32"/>
+      <c r="AK17" s="32">
+        <v>1</v>
+      </c>
       <c r="AL17" s="32"/>
       <c r="AM17" s="32"/>
       <c r="AN17" s="32"/>
@@ -9301,8 +9307,8 @@
       <c r="F18" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="G18" s="38"/>
-      <c r="H18" s="40"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="41"/>
       <c r="I18" s="9">
         <v>1</v>
       </c>
@@ -9381,7 +9387,9 @@
         <v>1</v>
       </c>
       <c r="AJ18" s="9"/>
-      <c r="AK18" s="9"/>
+      <c r="AK18" s="9">
+        <v>1</v>
+      </c>
       <c r="AL18" s="9"/>
       <c r="AM18" s="9"/>
       <c r="AN18" s="9"/>
@@ -9407,8 +9415,8 @@
       <c r="F19" s="32" t="s">
         <v>362</v>
       </c>
-      <c r="G19" s="38"/>
-      <c r="H19" s="40"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="41"/>
       <c r="I19" s="32">
         <v>1</v>
       </c>
@@ -9483,7 +9491,9 @@
         <v>1</v>
       </c>
       <c r="AJ19" s="32"/>
-      <c r="AK19" s="32"/>
+      <c r="AK19" s="32">
+        <v>1</v>
+      </c>
       <c r="AL19" s="32"/>
       <c r="AM19" s="32"/>
       <c r="AN19" s="32"/>
@@ -9509,8 +9519,8 @@
       <c r="F20" s="26" t="s">
         <v>358</v>
       </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="40"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="41"/>
       <c r="I20" s="26"/>
       <c r="J20" s="26"/>
       <c r="K20" s="26"/>
@@ -9565,8 +9575,8 @@
       <c r="F21" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="G21" s="38"/>
-      <c r="H21" s="40"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="41"/>
       <c r="I21" s="7">
         <v>1</v>
       </c>
@@ -9645,7 +9655,9 @@
       </c>
       <c r="AI21" s="7"/>
       <c r="AJ21" s="7"/>
-      <c r="AK21" s="7"/>
+      <c r="AK21" s="7">
+        <v>1</v>
+      </c>
       <c r="AL21" s="7"/>
       <c r="AM21" s="7"/>
       <c r="AN21" s="7"/>
@@ -9671,8 +9683,8 @@
       <c r="F22" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="40"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="41"/>
       <c r="I22" s="9">
         <v>1</v>
       </c>
@@ -9753,7 +9765,9 @@
       </c>
       <c r="AI22" s="9"/>
       <c r="AJ22" s="9"/>
-      <c r="AK22" s="9"/>
+      <c r="AK22" s="9">
+        <v>1</v>
+      </c>
       <c r="AL22" s="9"/>
       <c r="AM22" s="9"/>
       <c r="AN22" s="9"/>
@@ -9779,8 +9793,8 @@
       <c r="F23" s="32" t="s">
         <v>346</v>
       </c>
-      <c r="G23" s="38"/>
-      <c r="H23" s="40"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="41"/>
       <c r="I23" s="32">
         <v>1</v>
       </c>
@@ -9851,7 +9865,9 @@
         <v>1</v>
       </c>
       <c r="AJ23" s="32"/>
-      <c r="AK23" s="32"/>
+      <c r="AK23" s="32">
+        <v>1</v>
+      </c>
       <c r="AL23" s="32"/>
       <c r="AM23" s="32"/>
       <c r="AN23" s="32"/>
@@ -9877,8 +9893,8 @@
       <c r="F24" s="32" t="s">
         <v>342</v>
       </c>
-      <c r="G24" s="38"/>
-      <c r="H24" s="40"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="41"/>
       <c r="I24" s="32">
         <v>1</v>
       </c>
@@ -9955,7 +9971,9 @@
       <c r="AJ24" s="32">
         <v>1</v>
       </c>
-      <c r="AK24" s="32"/>
+      <c r="AK24" s="32">
+        <v>1</v>
+      </c>
       <c r="AL24" s="32"/>
       <c r="AM24" s="32"/>
       <c r="AN24" s="32"/>
@@ -9981,8 +9999,8 @@
       <c r="F25" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="G25" s="38"/>
-      <c r="H25" s="40"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="41"/>
       <c r="I25" s="26"/>
       <c r="J25" s="26"/>
       <c r="K25" s="26"/>
@@ -10037,8 +10055,8 @@
       <c r="F26" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="40"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="41"/>
       <c r="I26" s="9">
         <v>1</v>
       </c>
@@ -10143,8 +10161,8 @@
       <c r="F27" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="G27" s="38"/>
-      <c r="H27" s="40"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="41"/>
       <c r="I27" s="7">
         <v>1</v>
       </c>
@@ -10253,8 +10271,8 @@
       <c r="F28" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="G28" s="38"/>
-      <c r="H28" s="40"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="41"/>
       <c r="I28" s="9">
         <v>1</v>
       </c>
@@ -10357,8 +10375,8 @@
       <c r="F29" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="G29" s="38"/>
-      <c r="H29" s="40"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="41"/>
       <c r="I29" s="7">
         <v>1</v>
       </c>
@@ -10439,7 +10457,9 @@
       <c r="AJ29" s="7">
         <v>1</v>
       </c>
-      <c r="AK29" s="7"/>
+      <c r="AK29" s="7">
+        <v>1</v>
+      </c>
       <c r="AL29" s="7"/>
       <c r="AM29" s="7"/>
       <c r="AN29" s="7"/>
@@ -10465,8 +10485,8 @@
       <c r="F30" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="G30" s="38"/>
-      <c r="H30" s="40"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="41"/>
       <c r="I30" s="26"/>
       <c r="J30" s="26">
         <v>1</v>
@@ -10543,8 +10563,8 @@
       <c r="F31" s="26" t="s">
         <v>311</v>
       </c>
-      <c r="G31" s="38"/>
-      <c r="H31" s="40"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="41"/>
       <c r="I31" s="26"/>
       <c r="J31" s="26"/>
       <c r="K31" s="26"/>
@@ -10599,8 +10619,8 @@
       <c r="F32" s="26" t="s">
         <v>307</v>
       </c>
-      <c r="G32" s="38"/>
-      <c r="H32" s="40"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="41"/>
       <c r="I32" s="26"/>
       <c r="J32" s="26"/>
       <c r="K32" s="26"/>
@@ -10655,8 +10675,8 @@
       <c r="F33" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="G33" s="38"/>
-      <c r="H33" s="40"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="41"/>
       <c r="I33" s="7">
         <v>1</v>
       </c>
@@ -10728,8 +10748,12 @@
         <v>1</v>
       </c>
       <c r="AI33" s="7"/>
-      <c r="AJ33" s="7"/>
-      <c r="AK33" s="7"/>
+      <c r="AJ33" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK33" s="7">
+        <v>1</v>
+      </c>
       <c r="AL33" s="7"/>
       <c r="AM33" s="7"/>
       <c r="AN33" s="7"/>
@@ -10755,8 +10779,8 @@
       <c r="F34" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="G34" s="38"/>
-      <c r="H34" s="40"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="41"/>
       <c r="I34" s="26">
         <v>1</v>
       </c>
@@ -10839,8 +10863,8 @@
       <c r="F35" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="G35" s="38"/>
-      <c r="H35" s="40"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="41"/>
       <c r="I35" s="26"/>
       <c r="J35" s="26"/>
       <c r="K35" s="26"/>
@@ -10895,8 +10919,8 @@
       <c r="F36" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="G36" s="41"/>
-      <c r="H36" s="43"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="44"/>
       <c r="I36" s="32">
         <v>1</v>
       </c>
@@ -10973,7 +10997,9 @@
         <v>1</v>
       </c>
       <c r="AJ36" s="32"/>
-      <c r="AK36" s="32"/>
+      <c r="AK36" s="32">
+        <v>1</v>
+      </c>
       <c r="AL36" s="32"/>
       <c r="AM36" s="32"/>
       <c r="AN36" s="32"/>
@@ -11135,9 +11161,9 @@
       <c r="F3" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="37"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="38"/>
       <c r="J3" s="7">
         <v>1</v>
       </c>
@@ -11227,9 +11253,9 @@
       <c r="F4" s="9" t="s">
         <v>573</v>
       </c>
-      <c r="G4" s="38"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="40"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="41"/>
       <c r="J4" s="9"/>
       <c r="K4" s="9">
         <v>1</v>
@@ -11295,9 +11321,9 @@
       <c r="F5" s="7" t="s">
         <v>569</v>
       </c>
-      <c r="G5" s="38"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="40"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="41"/>
       <c r="J5" s="7">
         <v>1</v>
       </c>
@@ -11365,9 +11391,9 @@
       <c r="F6" s="9" t="s">
         <v>565</v>
       </c>
-      <c r="G6" s="38"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="40"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="41"/>
       <c r="J6" s="9">
         <v>1</v>
       </c>
@@ -11435,9 +11461,9 @@
       <c r="F7" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="G7" s="38"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="40"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="41"/>
       <c r="J7" s="7">
         <v>1</v>
       </c>
@@ -11505,9 +11531,9 @@
       <c r="F8" s="9" t="s">
         <v>557</v>
       </c>
-      <c r="G8" s="38"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="40"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
@@ -11561,9 +11587,9 @@
       <c r="F9" s="7" t="s">
         <v>553</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="40"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
@@ -11617,9 +11643,9 @@
       <c r="F10" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="40"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="41"/>
       <c r="J10" s="9">
         <v>1</v>
       </c>
@@ -11687,9 +11713,9 @@
       <c r="F11" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="G11" s="38"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="40"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="41"/>
       <c r="J11" s="7">
         <v>1</v>
       </c>
@@ -11757,9 +11783,9 @@
       <c r="F12" s="9" t="s">
         <v>541</v>
       </c>
-      <c r="G12" s="38"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="40"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="41"/>
       <c r="J12" s="9">
         <v>1</v>
       </c>
@@ -11827,9 +11853,9 @@
       <c r="F13" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="G13" s="38"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="40"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="41"/>
       <c r="J13" s="7">
         <v>1</v>
       </c>
@@ -11897,9 +11923,9 @@
       <c r="F14" s="9" t="s">
         <v>533</v>
       </c>
-      <c r="G14" s="38"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="40"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="41"/>
       <c r="J14" s="9">
         <v>1</v>
       </c>
@@ -11967,9 +11993,9 @@
       <c r="F15" s="7" t="s">
         <v>529</v>
       </c>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="41"/>
       <c r="J15" s="7">
         <v>1</v>
       </c>
@@ -12037,9 +12063,9 @@
       <c r="F16" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="G16" s="38"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="41"/>
       <c r="J16" s="9">
         <v>1</v>
       </c>
@@ -12107,9 +12133,9 @@
       <c r="F17" s="7" t="s">
         <v>521</v>
       </c>
-      <c r="G17" s="38"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="40"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="41"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7">
@@ -12165,9 +12191,9 @@
       <c r="F18" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="G18" s="38"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="40"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="41"/>
       <c r="J18" s="9">
         <v>1</v>
       </c>
@@ -12235,9 +12261,9 @@
       <c r="F19" s="7" t="s">
         <v>513</v>
       </c>
-      <c r="G19" s="38"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="41"/>
       <c r="J19" s="7">
         <v>1</v>
       </c>
@@ -12299,9 +12325,9 @@
       <c r="F20" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="40"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
@@ -12355,9 +12381,9 @@
       <c r="F21" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="G21" s="38"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="41"/>
       <c r="J21" s="7">
         <v>1</v>
       </c>
@@ -12425,9 +12451,9 @@
       <c r="F22" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="41"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
@@ -12481,9 +12507,9 @@
       <c r="F23" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="G23" s="38"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="41"/>
       <c r="J23" s="7">
         <v>1</v>
       </c>
@@ -12545,9 +12571,9 @@
       <c r="F24" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="G24" s="38"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="41"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="9">
@@ -12603,9 +12629,9 @@
       <c r="F25" s="7" t="s">
         <v>489</v>
       </c>
-      <c r="G25" s="38"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="41"/>
       <c r="J25" s="7">
         <v>1</v>
       </c>
@@ -12673,9 +12699,9 @@
       <c r="F26" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="41"/>
       <c r="J26" s="9">
         <v>1</v>
       </c>
@@ -12743,9 +12769,9 @@
       <c r="F27" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="41"/>
       <c r="J27" s="7">
         <v>1</v>
       </c>
@@ -12813,9 +12839,9 @@
       <c r="F28" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="G28" s="38"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="41"/>
       <c r="J28" s="9">
         <v>1</v>
       </c>
@@ -12905,9 +12931,9 @@
       <c r="F29" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="G29" s="38"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="41"/>
       <c r="J29" s="7">
         <v>1</v>
       </c>
@@ -12975,9 +13001,9 @@
       <c r="F30" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="G30" s="38"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="40"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="41"/>
       <c r="J30" s="9">
         <v>1</v>
       </c>
@@ -13045,9 +13071,9 @@
       <c r="F31" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="G31" s="38"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="40"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="41"/>
       <c r="J31" s="7">
         <v>1</v>
       </c>
@@ -13115,9 +13141,9 @@
       <c r="F32" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="G32" s="38"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="40"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="41"/>
       <c r="J32" s="9">
         <v>1</v>
       </c>
@@ -13185,9 +13211,9 @@
       <c r="F33" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="G33" s="38"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="40"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="41"/>
       <c r="J33" s="7">
         <v>1</v>
       </c>
@@ -13255,9 +13281,9 @@
       <c r="F34" s="9" t="s">
         <v>453</v>
       </c>
-      <c r="G34" s="38"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="40"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="41"/>
       <c r="J34" s="9">
         <v>1</v>
       </c>
@@ -13325,9 +13351,9 @@
       <c r="F35" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="G35" s="38"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="40"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="41"/>
       <c r="J35" s="7">
         <v>1</v>
       </c>
@@ -13395,9 +13421,9 @@
       <c r="F36" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="G36" s="38"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="40"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="41"/>
       <c r="J36" s="9">
         <v>1</v>
       </c>
@@ -13481,9 +13507,9 @@
       <c r="F37" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="G37" s="38"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="40"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="41"/>
       <c r="J37" s="7">
         <v>1</v>
       </c>
@@ -13551,9 +13577,9 @@
       <c r="F38" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="G38" s="38"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="40"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="41"/>
       <c r="J38" s="9">
         <v>1</v>
       </c>
@@ -13621,9 +13647,9 @@
       <c r="F39" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="G39" s="41"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="43"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="44"/>
       <c r="J39" s="7">
         <v>1</v>
       </c>
@@ -13874,9 +13900,9 @@
       <c r="F3" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="37"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="38"/>
       <c r="J3" s="7">
         <v>1</v>
       </c>
@@ -13984,9 +14010,9 @@
       <c r="F4" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="G4" s="38"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="40"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="41"/>
       <c r="J4" s="9">
         <v>1</v>
       </c>
@@ -14098,9 +14124,9 @@
       <c r="F5" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="G5" s="38"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="40"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="41"/>
       <c r="J5" s="7">
         <v>1</v>
       </c>
@@ -14210,9 +14236,9 @@
       <c r="F6" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="G6" s="38"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="40"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="41"/>
       <c r="J6" s="9">
         <v>1</v>
       </c>
@@ -14324,9 +14350,9 @@
       <c r="F7" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="G7" s="38"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="40"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="41"/>
       <c r="J7" s="7">
         <v>1</v>
       </c>
@@ -14438,9 +14464,9 @@
       <c r="F8" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="G8" s="38"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="40"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="9">
         <v>1</v>
       </c>
@@ -14552,9 +14578,9 @@
       <c r="F9" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="40"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="7">
         <v>1</v>
       </c>
@@ -14666,9 +14692,9 @@
       <c r="F10" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="40"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="41"/>
       <c r="J10" s="9">
         <v>1</v>
       </c>
@@ -14780,9 +14806,9 @@
       <c r="F11" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="G11" s="38"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="40"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="41"/>
       <c r="J11" s="26">
         <v>1</v>
       </c>
@@ -14876,9 +14902,9 @@
       <c r="F12" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="G12" s="38"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="40"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="41"/>
       <c r="J12" s="26">
         <v>1</v>
       </c>
@@ -14970,9 +14996,9 @@
       <c r="F13" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="G13" s="38"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="40"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="41"/>
       <c r="J13" s="7">
         <v>1</v>
       </c>
@@ -15084,9 +15110,9 @@
       <c r="F14" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="G14" s="38"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="40"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="41"/>
       <c r="J14" s="26">
         <v>1</v>
       </c>
@@ -15180,9 +15206,9 @@
       <c r="F15" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="41"/>
       <c r="J15" s="26">
         <v>1</v>
       </c>
@@ -15276,9 +15302,9 @@
       <c r="F16" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="G16" s="38"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="41"/>
       <c r="J16" s="9">
         <v>1</v>
       </c>
@@ -15390,9 +15416,9 @@
       <c r="F17" s="26" t="s">
         <v>229</v>
       </c>
-      <c r="G17" s="38"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="40"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="41"/>
       <c r="J17" s="26">
         <v>1</v>
       </c>
@@ -15484,9 +15510,9 @@
       <c r="F18" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="G18" s="38"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="40"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="41"/>
       <c r="J18" s="26"/>
       <c r="K18" s="26"/>
       <c r="L18" s="26"/>
@@ -15544,9 +15570,9 @@
       <c r="F19" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="G19" s="38"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="41"/>
       <c r="J19" s="26">
         <v>1</v>
       </c>
@@ -15640,9 +15666,9 @@
       <c r="F20" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="40"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
       <c r="J20" s="9">
         <v>1</v>
       </c>
@@ -15752,9 +15778,9 @@
       <c r="F21" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="G21" s="38"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="41"/>
       <c r="J21" s="7">
         <v>1</v>
       </c>
@@ -15864,9 +15890,9 @@
       <c r="F22" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="41"/>
       <c r="J22" s="9">
         <v>1</v>
       </c>
@@ -15976,9 +16002,9 @@
       <c r="F23" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="G23" s="38"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="41"/>
       <c r="J23" s="32">
         <v>1</v>
       </c>
@@ -16092,9 +16118,9 @@
       <c r="F24" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="G24" s="38"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="41"/>
       <c r="J24" s="9">
         <v>1</v>
       </c>
@@ -16206,9 +16232,9 @@
       <c r="F25" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="G25" s="38"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="41"/>
       <c r="J25" s="7">
         <v>1</v>
       </c>
@@ -16320,9 +16346,9 @@
       <c r="F26" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="41"/>
       <c r="J26" s="9">
         <v>1</v>
       </c>
@@ -16430,9 +16456,9 @@
       <c r="F27" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="41"/>
       <c r="J27" s="7">
         <v>1</v>
       </c>
@@ -16538,9 +16564,9 @@
       <c r="F28" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="G28" s="38"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="41"/>
       <c r="J28" s="26">
         <v>1</v>
       </c>
@@ -16612,9 +16638,9 @@
       <c r="F29" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="G29" s="38"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="41"/>
       <c r="J29" s="32">
         <v>1</v>
       </c>
@@ -16722,9 +16748,9 @@
       <c r="F30" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="G30" s="38"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="40"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="41"/>
       <c r="J30" s="9">
         <v>1</v>
       </c>
@@ -16836,9 +16862,9 @@
       <c r="F31" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="G31" s="38"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="40"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="41"/>
       <c r="J31" s="7">
         <v>1</v>
       </c>
@@ -16950,9 +16976,9 @@
       <c r="F32" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="G32" s="38"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="40"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="41"/>
       <c r="J32" s="9">
         <v>1</v>
       </c>
@@ -17060,9 +17086,9 @@
       <c r="F33" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="G33" s="38"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="40"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="41"/>
       <c r="J33" s="7">
         <v>1</v>
       </c>
@@ -17168,9 +17194,9 @@
       <c r="F34" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="G34" s="38"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="40"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="41"/>
       <c r="J34" s="26">
         <v>1</v>
       </c>
@@ -17260,9 +17286,9 @@
       <c r="F35" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="G35" s="38"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="40"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="41"/>
       <c r="J35" s="26">
         <v>1</v>
       </c>
@@ -17356,9 +17382,9 @@
       <c r="F36" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="G36" s="38"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="40"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="41"/>
       <c r="J36" s="9">
         <v>1</v>
       </c>
@@ -17470,9 +17496,9 @@
       <c r="F37" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="G37" s="38"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="40"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="41"/>
       <c r="J37" s="7">
         <v>1</v>
       </c>
@@ -17584,9 +17610,9 @@
       <c r="F38" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="G38" s="38"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="40"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="41"/>
       <c r="J38" s="9">
         <v>1</v>
       </c>
@@ -17692,9 +17718,9 @@
       <c r="F39" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="G39" s="38"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="40"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="41"/>
       <c r="J39" s="32">
         <v>1</v>
       </c>
@@ -17776,9 +17802,9 @@
       </c>
       <c r="E40" s="28"/>
       <c r="F40" s="26"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="40"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="41"/>
       <c r="J40" s="26"/>
       <c r="K40" s="26"/>
       <c r="L40" s="26"/>
@@ -18098,8 +18124,8 @@
       <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="44"/>
-      <c r="H3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="46"/>
       <c r="I3" s="2">
         <v>1</v>
       </c>
@@ -18202,8 +18228,8 @@
       <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="46"/>
-      <c r="H4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="48"/>
       <c r="I4" s="3">
         <v>1</v>
       </c>
@@ -18310,8 +18336,8 @@
       <c r="F5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="46"/>
-      <c r="H5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="48"/>
       <c r="I5" s="2">
         <v>1</v>
       </c>
@@ -18418,8 +18444,8 @@
       <c r="F6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="46"/>
-      <c r="H6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="48"/>
       <c r="I6" s="3">
         <v>1</v>
       </c>
@@ -18526,8 +18552,8 @@
       <c r="F7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="48"/>
       <c r="I7" s="2">
         <v>1</v>
       </c>
@@ -18632,8 +18658,8 @@
       <c r="F8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="48"/>
       <c r="I8" s="3">
         <v>1</v>
       </c>
@@ -18740,8 +18766,8 @@
       <c r="F9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="46"/>
-      <c r="H9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
       <c r="I9" s="2">
         <v>1</v>
       </c>
@@ -18848,8 +18874,8 @@
       <c r="F10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="46"/>
-      <c r="H10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="48"/>
       <c r="I10" s="3">
         <v>1</v>
       </c>
@@ -18956,8 +18982,8 @@
       <c r="F11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="46"/>
-      <c r="H11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="48"/>
       <c r="I11" s="2">
         <v>1</v>
       </c>
@@ -19064,8 +19090,8 @@
       <c r="F12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="46"/>
-      <c r="H12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="48"/>
       <c r="I12" s="3">
         <v>1</v>
       </c>
@@ -19150,8 +19176,8 @@
       <c r="F13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="46"/>
-      <c r="H13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="48"/>
       <c r="I13" s="2">
         <v>1</v>
       </c>
@@ -19258,8 +19284,8 @@
       <c r="F14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="46"/>
-      <c r="H14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="48"/>
       <c r="I14" s="3">
         <v>1</v>
       </c>
@@ -19358,8 +19384,8 @@
       <c r="F15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G15" s="46"/>
-      <c r="H15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="48"/>
       <c r="I15" s="2">
         <v>1</v>
       </c>
@@ -19464,8 +19490,8 @@
       <c r="F16" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G16" s="46"/>
-      <c r="H16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="48"/>
       <c r="I16" s="3">
         <v>1</v>
       </c>
@@ -19570,8 +19596,8 @@
       <c r="F17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="46"/>
-      <c r="H17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="48"/>
       <c r="I17" s="2">
         <v>1</v>
       </c>
@@ -19678,8 +19704,8 @@
       <c r="F18" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G18" s="46"/>
-      <c r="H18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="48"/>
       <c r="I18" s="3">
         <v>1</v>
       </c>
@@ -19782,8 +19808,8 @@
       <c r="F19" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G19" s="46"/>
-      <c r="H19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="48"/>
       <c r="I19" s="2">
         <v>1</v>
       </c>
@@ -19890,8 +19916,8 @@
       <c r="F20" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G20" s="46"/>
-      <c r="H20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="48"/>
       <c r="I20" s="3">
         <v>1</v>
       </c>
@@ -19998,8 +20024,8 @@
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G21" s="46"/>
-      <c r="H21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="48"/>
       <c r="I21" s="2">
         <v>1</v>
       </c>
@@ -20106,8 +20132,8 @@
       <c r="F22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G22" s="46"/>
-      <c r="H22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="48"/>
       <c r="I22" s="3">
         <v>1</v>
       </c>
@@ -20200,8 +20226,8 @@
       <c r="F23" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G23" s="46"/>
-      <c r="H23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="48"/>
       <c r="I23" s="2">
         <v>1</v>
       </c>
@@ -20308,8 +20334,8 @@
       <c r="F24" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="G24" s="46"/>
-      <c r="H24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="48"/>
       <c r="I24" s="3">
         <v>1</v>
       </c>
@@ -20414,8 +20440,8 @@
       <c r="F25" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G25" s="46"/>
-      <c r="H25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="48"/>
       <c r="I25" s="2">
         <v>1</v>
       </c>
@@ -20522,8 +20548,8 @@
       <c r="F26" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G26" s="46"/>
-      <c r="H26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="48"/>
       <c r="I26" s="3">
         <v>1</v>
       </c>
@@ -20630,8 +20656,8 @@
       <c r="F27" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G27" s="46"/>
-      <c r="H27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="48"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -20686,8 +20712,8 @@
       <c r="F28" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G28" s="46"/>
-      <c r="H28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="48"/>
       <c r="I28" s="3">
         <v>1</v>
       </c>
@@ -20794,8 +20820,8 @@
       <c r="F29" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G29" s="46"/>
-      <c r="H29" s="47"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="48"/>
       <c r="I29" s="2">
         <v>1</v>
       </c>
@@ -20902,8 +20928,8 @@
       <c r="F30" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G30" s="46"/>
-      <c r="H30" s="47"/>
+      <c r="G30" s="47"/>
+      <c r="H30" s="48"/>
       <c r="I30" s="3">
         <v>1</v>
       </c>
@@ -21008,8 +21034,8 @@
       <c r="F31" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G31" s="46"/>
-      <c r="H31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="48"/>
       <c r="I31" s="2">
         <v>1</v>
       </c>
@@ -21116,8 +21142,8 @@
       <c r="F32" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G32" s="46"/>
-      <c r="H32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="48"/>
       <c r="I32" s="3">
         <v>1</v>
       </c>
@@ -21224,8 +21250,8 @@
       <c r="F33" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G33" s="46"/>
-      <c r="H33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="48"/>
       <c r="I33" s="2">
         <v>1</v>
       </c>
@@ -21332,8 +21358,8 @@
       <c r="F34" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G34" s="48"/>
-      <c r="H34" s="49"/>
+      <c r="G34" s="49"/>
+      <c r="H34" s="50"/>
       <c r="I34" s="3">
         <v>1</v>
       </c>
@@ -21585,8 +21611,8 @@
       <c r="F3" s="26" t="s">
         <v>1031</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="37"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="38"/>
       <c r="I3" s="26"/>
       <c r="J3" s="26"/>
       <c r="K3" s="26"/>
@@ -21641,8 +21667,8 @@
       <c r="F4" s="9" t="s">
         <v>1027</v>
       </c>
-      <c r="G4" s="38"/>
-      <c r="H4" s="40"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="41"/>
       <c r="I4" s="9">
         <v>1</v>
       </c>
@@ -21749,8 +21775,8 @@
       <c r="F5" s="7" t="s">
         <v>1023</v>
       </c>
-      <c r="G5" s="38"/>
-      <c r="H5" s="40"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="41"/>
       <c r="I5" s="7">
         <v>1</v>
       </c>
@@ -21857,8 +21883,8 @@
       <c r="F6" s="9" t="s">
         <v>1019</v>
       </c>
-      <c r="G6" s="38"/>
-      <c r="H6" s="40"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="41"/>
       <c r="I6" s="9">
         <v>1</v>
       </c>
@@ -21965,8 +21991,8 @@
       <c r="F7" s="7" t="s">
         <v>1015</v>
       </c>
-      <c r="G7" s="38"/>
-      <c r="H7" s="40"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="41"/>
       <c r="I7" s="7">
         <v>1</v>
       </c>
@@ -22073,8 +22099,8 @@
       <c r="F8" s="9" t="s">
         <v>1011</v>
       </c>
-      <c r="G8" s="38"/>
-      <c r="H8" s="40"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="41"/>
       <c r="I8" s="9">
         <v>1</v>
       </c>
@@ -22181,8 +22207,8 @@
       <c r="F9" s="7" t="s">
         <v>1007</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="40"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="41"/>
       <c r="I9" s="7">
         <v>1</v>
       </c>
@@ -22289,8 +22315,8 @@
       <c r="F10" s="26" t="s">
         <v>1003</v>
       </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="40"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="41"/>
       <c r="I10" s="26"/>
       <c r="J10" s="26"/>
       <c r="K10" s="26"/>
@@ -22345,8 +22371,8 @@
       <c r="F11" s="7" t="s">
         <v>999</v>
       </c>
-      <c r="G11" s="38"/>
-      <c r="H11" s="40"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="41"/>
       <c r="I11" s="7">
         <v>1</v>
       </c>
@@ -22453,8 +22479,8 @@
       <c r="F12" s="9" t="s">
         <v>995</v>
       </c>
-      <c r="G12" s="38"/>
-      <c r="H12" s="40"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="41"/>
       <c r="I12" s="9">
         <v>1</v>
       </c>
@@ -22561,8 +22587,8 @@
       <c r="F13" s="7" t="s">
         <v>991</v>
       </c>
-      <c r="G13" s="38"/>
-      <c r="H13" s="40"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="41"/>
       <c r="I13" s="7">
         <v>1</v>
       </c>
@@ -22667,8 +22693,8 @@
       <c r="F14" s="9" t="s">
         <v>987</v>
       </c>
-      <c r="G14" s="38"/>
-      <c r="H14" s="40"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="41"/>
       <c r="I14" s="9">
         <v>1</v>
       </c>
@@ -22775,8 +22801,8 @@
       <c r="F15" s="26" t="s">
         <v>983</v>
       </c>
-      <c r="G15" s="38"/>
-      <c r="H15" s="40"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="41"/>
       <c r="I15" s="26"/>
       <c r="J15" s="26"/>
       <c r="K15" s="26"/>
@@ -22831,8 +22857,8 @@
       <c r="F16" s="9" t="s">
         <v>979</v>
       </c>
-      <c r="G16" s="38"/>
-      <c r="H16" s="40"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="41"/>
       <c r="I16" s="9">
         <v>1</v>
       </c>
@@ -22939,8 +22965,8 @@
       <c r="F17" s="26" t="s">
         <v>975</v>
       </c>
-      <c r="G17" s="38"/>
-      <c r="H17" s="40"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="41"/>
       <c r="I17" s="26"/>
       <c r="J17" s="26"/>
       <c r="K17" s="26"/>
@@ -22995,8 +23021,8 @@
       <c r="F18" s="9" t="s">
         <v>971</v>
       </c>
-      <c r="G18" s="38"/>
-      <c r="H18" s="40"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="41"/>
       <c r="I18" s="9">
         <v>1</v>
       </c>
@@ -23103,8 +23129,8 @@
       <c r="F19" s="7" t="s">
         <v>967</v>
       </c>
-      <c r="G19" s="38"/>
-      <c r="H19" s="40"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="41"/>
       <c r="I19" s="7">
         <v>1</v>
       </c>
@@ -23205,8 +23231,8 @@
       <c r="F20" s="9" t="s">
         <v>963</v>
       </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="40"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="41"/>
       <c r="I20" s="9">
         <v>1</v>
       </c>
@@ -23313,8 +23339,8 @@
       <c r="F21" s="26" t="s">
         <v>959</v>
       </c>
-      <c r="G21" s="38"/>
-      <c r="H21" s="40"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="41"/>
       <c r="I21" s="26"/>
       <c r="J21" s="26"/>
       <c r="K21" s="26"/>
@@ -23369,8 +23395,8 @@
       <c r="F22" s="9" t="s">
         <v>955</v>
       </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="40"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="41"/>
       <c r="I22" s="9">
         <v>1</v>
       </c>
@@ -23477,8 +23503,8 @@
       <c r="F23" s="7" t="s">
         <v>951</v>
       </c>
-      <c r="G23" s="38"/>
-      <c r="H23" s="40"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="41"/>
       <c r="I23" s="7">
         <v>1</v>
       </c>
@@ -23585,8 +23611,8 @@
       <c r="F24" s="9" t="s">
         <v>947</v>
       </c>
-      <c r="G24" s="38"/>
-      <c r="H24" s="40"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="41"/>
       <c r="I24" s="9">
         <v>1</v>
       </c>
@@ -23689,8 +23715,8 @@
       <c r="F25" s="7" t="s">
         <v>943</v>
       </c>
-      <c r="G25" s="41"/>
-      <c r="H25" s="43"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="44"/>
       <c r="I25" s="7">
         <v>1</v>
       </c>
@@ -23949,18 +23975,18 @@
       <c r="F3" s="7" t="s">
         <v>802</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="37"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="38"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="37"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="38"/>
       <c r="L3" s="7">
         <v>1</v>
       </c>
-      <c r="M3" s="50"/>
+      <c r="M3" s="51"/>
       <c r="N3" s="7"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="37"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="38"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
@@ -24016,18 +24042,18 @@
       <c r="F4" s="9" t="s">
         <v>798</v>
       </c>
-      <c r="G4" s="38"/>
-      <c r="H4" s="40"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="41"/>
       <c r="I4" s="9"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="40"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="41"/>
       <c r="L4" s="9">
         <v>1</v>
       </c>
-      <c r="M4" s="51"/>
+      <c r="M4" s="52"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="40"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="41"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
@@ -24083,18 +24109,18 @@
       <c r="F5" s="7" t="s">
         <v>794</v>
       </c>
-      <c r="G5" s="38"/>
-      <c r="H5" s="40"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="41"/>
       <c r="I5" s="7"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="40"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="41"/>
       <c r="L5" s="7">
         <v>1</v>
       </c>
-      <c r="M5" s="51"/>
+      <c r="M5" s="52"/>
       <c r="N5" s="7"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="40"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="41"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -24150,16 +24176,16 @@
       <c r="F6" s="9" t="s">
         <v>790</v>
       </c>
-      <c r="G6" s="38"/>
-      <c r="H6" s="40"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="41"/>
       <c r="I6" s="9"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="40"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="41"/>
       <c r="L6" s="9"/>
-      <c r="M6" s="51"/>
+      <c r="M6" s="52"/>
       <c r="N6" s="9"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="40"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="41"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
@@ -24215,18 +24241,18 @@
       <c r="F7" s="7" t="s">
         <v>786</v>
       </c>
-      <c r="G7" s="38"/>
-      <c r="H7" s="40"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="41"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="40"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="41"/>
       <c r="L7" s="7">
         <v>1</v>
       </c>
-      <c r="M7" s="51"/>
+      <c r="M7" s="52"/>
       <c r="N7" s="7"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="40"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="41"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
@@ -24282,18 +24308,18 @@
       <c r="F8" s="9" t="s">
         <v>782</v>
       </c>
-      <c r="G8" s="38"/>
-      <c r="H8" s="40"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="41"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="40"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="41"/>
       <c r="L8" s="9">
         <v>1</v>
       </c>
-      <c r="M8" s="51"/>
+      <c r="M8" s="52"/>
       <c r="N8" s="9"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="40"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="41"/>
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
@@ -24349,18 +24375,18 @@
       <c r="F9" s="7" t="s">
         <v>778</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="40"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="41"/>
       <c r="I9" s="7"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="40"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="41"/>
       <c r="L9" s="7">
         <v>1</v>
       </c>
-      <c r="M9" s="51"/>
+      <c r="M9" s="52"/>
       <c r="N9" s="7"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="40"/>
+      <c r="O9" s="39"/>
+      <c r="P9" s="41"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
@@ -24416,18 +24442,18 @@
       <c r="F10" s="9" t="s">
         <v>774</v>
       </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="40"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="41"/>
       <c r="I10" s="9"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="40"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="41"/>
       <c r="L10" s="9">
         <v>1</v>
       </c>
-      <c r="M10" s="51"/>
+      <c r="M10" s="52"/>
       <c r="N10" s="9"/>
-      <c r="O10" s="38"/>
-      <c r="P10" s="40"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="41"/>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
       <c r="S10" s="9"/>
@@ -24483,18 +24509,18 @@
       <c r="F11" s="7" t="s">
         <v>770</v>
       </c>
-      <c r="G11" s="38"/>
-      <c r="H11" s="40"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="41"/>
       <c r="I11" s="7"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="40"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="41"/>
       <c r="L11" s="7">
         <v>1</v>
       </c>
-      <c r="M11" s="51"/>
+      <c r="M11" s="52"/>
       <c r="N11" s="7"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="40"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="41"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
@@ -24550,18 +24576,18 @@
       <c r="F12" s="9" t="s">
         <v>766</v>
       </c>
-      <c r="G12" s="38"/>
-      <c r="H12" s="40"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="41"/>
       <c r="I12" s="9"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="40"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="41"/>
       <c r="L12" s="9">
         <v>1</v>
       </c>
-      <c r="M12" s="51"/>
+      <c r="M12" s="52"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="40"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="41"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
@@ -24617,16 +24643,16 @@
       <c r="F13" s="7" t="s">
         <v>762</v>
       </c>
-      <c r="G13" s="38"/>
-      <c r="H13" s="40"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="41"/>
       <c r="I13" s="7"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="40"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="41"/>
       <c r="L13" s="7"/>
-      <c r="M13" s="51"/>
+      <c r="M13" s="52"/>
       <c r="N13" s="7"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="40"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="41"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
@@ -24682,18 +24708,18 @@
       <c r="F14" s="9" t="s">
         <v>758</v>
       </c>
-      <c r="G14" s="38"/>
-      <c r="H14" s="40"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="41"/>
       <c r="I14" s="9"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="40"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="41"/>
       <c r="L14" s="9">
         <v>1</v>
       </c>
-      <c r="M14" s="51"/>
+      <c r="M14" s="52"/>
       <c r="N14" s="9"/>
-      <c r="O14" s="38"/>
-      <c r="P14" s="40"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="41"/>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
@@ -24749,16 +24775,16 @@
       <c r="F15" s="7" t="s">
         <v>754</v>
       </c>
-      <c r="G15" s="38"/>
-      <c r="H15" s="40"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="41"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="40"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="41"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="51"/>
+      <c r="M15" s="52"/>
       <c r="N15" s="7"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="40"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="41"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
@@ -24814,18 +24840,18 @@
       <c r="F16" s="9" t="s">
         <v>750</v>
       </c>
-      <c r="G16" s="38"/>
-      <c r="H16" s="40"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="41"/>
       <c r="I16" s="9"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="40"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="41"/>
       <c r="L16" s="9">
         <v>1</v>
       </c>
-      <c r="M16" s="51"/>
+      <c r="M16" s="52"/>
       <c r="N16" s="9"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="40"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="41"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
@@ -24881,18 +24907,18 @@
       <c r="F17" s="7" t="s">
         <v>746</v>
       </c>
-      <c r="G17" s="38"/>
-      <c r="H17" s="40"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="41"/>
       <c r="I17" s="7"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="40"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="41"/>
       <c r="L17" s="7">
         <v>1</v>
       </c>
-      <c r="M17" s="51"/>
+      <c r="M17" s="52"/>
       <c r="N17" s="7"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="40"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="41"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
@@ -24948,18 +24974,18 @@
       <c r="F18" s="9" t="s">
         <v>742</v>
       </c>
-      <c r="G18" s="38"/>
-      <c r="H18" s="40"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="41"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="40"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="41"/>
       <c r="L18" s="9">
         <v>1</v>
       </c>
-      <c r="M18" s="51"/>
+      <c r="M18" s="52"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="38"/>
-      <c r="P18" s="40"/>
+      <c r="O18" s="39"/>
+      <c r="P18" s="41"/>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
@@ -25015,18 +25041,18 @@
       <c r="F19" s="7" t="s">
         <v>738</v>
       </c>
-      <c r="G19" s="38"/>
-      <c r="H19" s="40"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="41"/>
       <c r="I19" s="7"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="40"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="41"/>
       <c r="L19" s="7">
         <v>1</v>
       </c>
-      <c r="M19" s="51"/>
+      <c r="M19" s="52"/>
       <c r="N19" s="7"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="40"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="41"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
@@ -25082,18 +25108,18 @@
       <c r="F20" s="9" t="s">
         <v>734</v>
       </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="40"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="41"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="40"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="41"/>
       <c r="L20" s="9">
         <v>1</v>
       </c>
-      <c r="M20" s="51"/>
+      <c r="M20" s="52"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="40"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="41"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
       <c r="S20" s="9"/>
@@ -25149,16 +25175,16 @@
       <c r="F21" s="7" t="s">
         <v>730</v>
       </c>
-      <c r="G21" s="38"/>
-      <c r="H21" s="40"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="41"/>
       <c r="I21" s="7"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="40"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="41"/>
       <c r="L21" s="7"/>
-      <c r="M21" s="51"/>
+      <c r="M21" s="52"/>
       <c r="N21" s="7"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="40"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="41"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
@@ -25214,16 +25240,16 @@
       <c r="F22" s="9" t="s">
         <v>726</v>
       </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="40"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="41"/>
       <c r="I22" s="9"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="40"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="41"/>
       <c r="L22" s="9"/>
-      <c r="M22" s="51"/>
+      <c r="M22" s="52"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="38"/>
-      <c r="P22" s="40"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="41"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
       <c r="S22" s="9"/>
@@ -25279,18 +25305,18 @@
       <c r="F23" s="7" t="s">
         <v>722</v>
       </c>
-      <c r="G23" s="38"/>
-      <c r="H23" s="40"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="41"/>
       <c r="I23" s="7"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="40"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="41"/>
       <c r="L23" s="7">
         <v>1</v>
       </c>
-      <c r="M23" s="51"/>
+      <c r="M23" s="52"/>
       <c r="N23" s="7"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="40"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="41"/>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
@@ -25346,18 +25372,18 @@
       <c r="F24" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="G24" s="38"/>
-      <c r="H24" s="40"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="41"/>
       <c r="I24" s="9"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="40"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="41"/>
       <c r="L24" s="9">
         <v>1</v>
       </c>
-      <c r="M24" s="51"/>
+      <c r="M24" s="52"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="38"/>
-      <c r="P24" s="40"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="41"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
       <c r="S24" s="9"/>
@@ -25413,18 +25439,18 @@
       <c r="F25" s="7" t="s">
         <v>714</v>
       </c>
-      <c r="G25" s="38"/>
-      <c r="H25" s="40"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="41"/>
       <c r="I25" s="7"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="40"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="41"/>
       <c r="L25" s="7">
         <v>1</v>
       </c>
-      <c r="M25" s="51"/>
+      <c r="M25" s="52"/>
       <c r="N25" s="7"/>
-      <c r="O25" s="38"/>
-      <c r="P25" s="40"/>
+      <c r="O25" s="39"/>
+      <c r="P25" s="41"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
@@ -25480,16 +25506,16 @@
       <c r="F26" s="9" t="s">
         <v>710</v>
       </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="40"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="41"/>
       <c r="I26" s="9"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="40"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="41"/>
       <c r="L26" s="9"/>
-      <c r="M26" s="51"/>
+      <c r="M26" s="52"/>
       <c r="N26" s="9"/>
-      <c r="O26" s="38"/>
-      <c r="P26" s="40"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="41"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
       <c r="S26" s="9"/>
@@ -25545,18 +25571,18 @@
       <c r="F27" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="G27" s="38"/>
-      <c r="H27" s="40"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="41"/>
       <c r="I27" s="7"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="40"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="41"/>
       <c r="L27" s="7">
         <v>1</v>
       </c>
-      <c r="M27" s="51"/>
+      <c r="M27" s="52"/>
       <c r="N27" s="7"/>
-      <c r="O27" s="38"/>
-      <c r="P27" s="40"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="41"/>
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
@@ -25612,18 +25638,18 @@
       <c r="F28" s="9" t="s">
         <v>702</v>
       </c>
-      <c r="G28" s="38"/>
-      <c r="H28" s="40"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="41"/>
       <c r="I28" s="9"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="40"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="41"/>
       <c r="L28" s="9">
         <v>1</v>
       </c>
-      <c r="M28" s="51"/>
+      <c r="M28" s="52"/>
       <c r="N28" s="9"/>
-      <c r="O28" s="38"/>
-      <c r="P28" s="40"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="41"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
       <c r="S28" s="9"/>
@@ -25679,18 +25705,18 @@
       <c r="F29" s="7" t="s">
         <v>698</v>
       </c>
-      <c r="G29" s="38"/>
-      <c r="H29" s="40"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="41"/>
       <c r="I29" s="7"/>
-      <c r="J29" s="38"/>
-      <c r="K29" s="40"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="41"/>
       <c r="L29" s="7">
         <v>1</v>
       </c>
-      <c r="M29" s="51"/>
+      <c r="M29" s="52"/>
       <c r="N29" s="7"/>
-      <c r="O29" s="38"/>
-      <c r="P29" s="40"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="41"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
@@ -25746,16 +25772,16 @@
       <c r="F30" s="9" t="s">
         <v>694</v>
       </c>
-      <c r="G30" s="38"/>
-      <c r="H30" s="40"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="41"/>
       <c r="I30" s="9"/>
-      <c r="J30" s="38"/>
-      <c r="K30" s="40"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="41"/>
       <c r="L30" s="9"/>
-      <c r="M30" s="51"/>
+      <c r="M30" s="52"/>
       <c r="N30" s="9"/>
-      <c r="O30" s="38"/>
-      <c r="P30" s="40"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="41"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
       <c r="S30" s="9"/>
@@ -25811,18 +25837,18 @@
       <c r="F31" s="7" t="s">
         <v>690</v>
       </c>
-      <c r="G31" s="38"/>
-      <c r="H31" s="40"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="41"/>
       <c r="I31" s="7"/>
-      <c r="J31" s="38"/>
-      <c r="K31" s="40"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="41"/>
       <c r="L31" s="7">
         <v>1</v>
       </c>
-      <c r="M31" s="51"/>
+      <c r="M31" s="52"/>
       <c r="N31" s="7"/>
-      <c r="O31" s="38"/>
-      <c r="P31" s="40"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="41"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
       <c r="S31" s="7"/>
@@ -25878,18 +25904,18 @@
       <c r="F32" s="9" t="s">
         <v>686</v>
       </c>
-      <c r="G32" s="38"/>
-      <c r="H32" s="40"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="41"/>
       <c r="I32" s="9"/>
-      <c r="J32" s="38"/>
-      <c r="K32" s="40"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="41"/>
       <c r="L32" s="9">
         <v>1</v>
       </c>
-      <c r="M32" s="51"/>
+      <c r="M32" s="52"/>
       <c r="N32" s="9"/>
-      <c r="O32" s="38"/>
-      <c r="P32" s="40"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="41"/>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
       <c r="S32" s="9"/>
@@ -25945,18 +25971,18 @@
       <c r="F33" s="7" t="s">
         <v>682</v>
       </c>
-      <c r="G33" s="38"/>
-      <c r="H33" s="40"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="41"/>
       <c r="I33" s="7"/>
-      <c r="J33" s="38"/>
-      <c r="K33" s="40"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="41"/>
       <c r="L33" s="7">
         <v>1</v>
       </c>
-      <c r="M33" s="51"/>
+      <c r="M33" s="52"/>
       <c r="N33" s="7"/>
-      <c r="O33" s="38"/>
-      <c r="P33" s="40"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="41"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
       <c r="S33" s="7"/>
@@ -26012,18 +26038,18 @@
       <c r="F34" s="9" t="s">
         <v>678</v>
       </c>
-      <c r="G34" s="38"/>
-      <c r="H34" s="40"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="41"/>
       <c r="I34" s="9"/>
-      <c r="J34" s="38"/>
-      <c r="K34" s="40"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="41"/>
       <c r="L34" s="9">
         <v>1</v>
       </c>
-      <c r="M34" s="51"/>
+      <c r="M34" s="52"/>
       <c r="N34" s="9"/>
-      <c r="O34" s="38"/>
-      <c r="P34" s="40"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="41"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
       <c r="S34" s="9"/>
@@ -26079,18 +26105,18 @@
       <c r="F35" s="7" t="s">
         <v>674</v>
       </c>
-      <c r="G35" s="38"/>
-      <c r="H35" s="40"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="41"/>
       <c r="I35" s="7"/>
-      <c r="J35" s="38"/>
-      <c r="K35" s="40"/>
+      <c r="J35" s="39"/>
+      <c r="K35" s="41"/>
       <c r="L35" s="7">
         <v>1</v>
       </c>
-      <c r="M35" s="51"/>
+      <c r="M35" s="52"/>
       <c r="N35" s="7"/>
-      <c r="O35" s="38"/>
-      <c r="P35" s="40"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="41"/>
       <c r="Q35" s="7"/>
       <c r="R35" s="7"/>
       <c r="S35" s="7"/>
@@ -26146,18 +26172,18 @@
       <c r="F36" s="9" t="s">
         <v>670</v>
       </c>
-      <c r="G36" s="38"/>
-      <c r="H36" s="40"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="41"/>
       <c r="I36" s="9"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="40"/>
+      <c r="J36" s="39"/>
+      <c r="K36" s="41"/>
       <c r="L36" s="9">
         <v>1</v>
       </c>
-      <c r="M36" s="51"/>
+      <c r="M36" s="52"/>
       <c r="N36" s="9"/>
-      <c r="O36" s="38"/>
-      <c r="P36" s="40"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="41"/>
       <c r="Q36" s="9"/>
       <c r="R36" s="9"/>
       <c r="S36" s="9"/>
@@ -26213,18 +26239,18 @@
       <c r="F37" s="7" t="s">
         <v>666</v>
       </c>
-      <c r="G37" s="38"/>
-      <c r="H37" s="40"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="41"/>
       <c r="I37" s="7"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="40"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="41"/>
       <c r="L37" s="7">
         <v>1</v>
       </c>
-      <c r="M37" s="51"/>
+      <c r="M37" s="52"/>
       <c r="N37" s="7"/>
-      <c r="O37" s="38"/>
-      <c r="P37" s="40"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="41"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="7"/>
       <c r="S37" s="7"/>
@@ -26280,18 +26306,18 @@
       <c r="F38" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="G38" s="38"/>
-      <c r="H38" s="40"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="41"/>
       <c r="I38" s="9"/>
-      <c r="J38" s="38"/>
-      <c r="K38" s="40"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="41"/>
       <c r="L38" s="9">
         <v>1</v>
       </c>
-      <c r="M38" s="51"/>
+      <c r="M38" s="52"/>
       <c r="N38" s="9"/>
-      <c r="O38" s="38"/>
-      <c r="P38" s="40"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="41"/>
       <c r="Q38" s="9"/>
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
@@ -26347,16 +26373,16 @@
       <c r="F39" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="G39" s="38"/>
-      <c r="H39" s="40"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="41"/>
       <c r="I39" s="7"/>
-      <c r="J39" s="38"/>
-      <c r="K39" s="40"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="41"/>
       <c r="L39" s="7"/>
-      <c r="M39" s="51"/>
+      <c r="M39" s="52"/>
       <c r="N39" s="7"/>
-      <c r="O39" s="38"/>
-      <c r="P39" s="40"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="41"/>
       <c r="Q39" s="7"/>
       <c r="R39" s="7"/>
       <c r="S39" s="7"/>
@@ -26412,18 +26438,18 @@
       <c r="F40" s="9" t="s">
         <v>654</v>
       </c>
-      <c r="G40" s="41"/>
-      <c r="H40" s="43"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="44"/>
       <c r="I40" s="9"/>
-      <c r="J40" s="41"/>
-      <c r="K40" s="43"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="44"/>
       <c r="L40" s="9">
         <v>1</v>
       </c>
-      <c r="M40" s="52"/>
+      <c r="M40" s="53"/>
       <c r="N40" s="9"/>
-      <c r="O40" s="41"/>
-      <c r="P40" s="43"/>
+      <c r="O40" s="42"/>
+      <c r="P40" s="44"/>
       <c r="Q40" s="9"/>
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
@@ -26609,17 +26635,17 @@
       <c r="D3" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E3" s="35"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="37"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="38"/>
       <c r="H3" s="7"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="37"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="38"/>
       <c r="K3" s="7"/>
-      <c r="L3" s="50"/>
+      <c r="L3" s="51"/>
       <c r="M3" s="7"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="37"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="38"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -26659,17 +26685,17 @@
       <c r="D4" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E4" s="38"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="40"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="41"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="40"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="41"/>
       <c r="K4" s="9"/>
-      <c r="L4" s="51"/>
+      <c r="L4" s="52"/>
       <c r="M4" s="9"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="40"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="41"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
@@ -26709,17 +26735,17 @@
       <c r="D5" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E5" s="38"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="40"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="41"/>
       <c r="H5" s="7"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="40"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="41"/>
       <c r="K5" s="7"/>
-      <c r="L5" s="51"/>
+      <c r="L5" s="52"/>
       <c r="M5" s="7"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="40"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="41"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
@@ -26759,17 +26785,17 @@
       <c r="D6" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E6" s="38"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="40"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="41"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="40"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="41"/>
       <c r="K6" s="9"/>
-      <c r="L6" s="51"/>
+      <c r="L6" s="52"/>
       <c r="M6" s="9"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="40"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="41"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
@@ -26809,17 +26835,17 @@
       <c r="D7" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E7" s="38"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="40"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="41"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="40"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="41"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="51"/>
+      <c r="L7" s="52"/>
       <c r="M7" s="7"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="40"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="41"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
@@ -26859,17 +26885,17 @@
       <c r="D8" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="41"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="40"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="41"/>
       <c r="K8" s="9"/>
-      <c r="L8" s="51"/>
+      <c r="L8" s="52"/>
       <c r="M8" s="9"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="40"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="41"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
@@ -26909,17 +26935,17 @@
       <c r="D9" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E9" s="38"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="41"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="40"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="41"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="51"/>
+      <c r="L9" s="52"/>
       <c r="M9" s="7"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="40"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="41"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
@@ -26959,17 +26985,17 @@
       <c r="D10" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E10" s="38"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="40"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="41"/>
       <c r="K10" s="9"/>
-      <c r="L10" s="51"/>
+      <c r="L10" s="52"/>
       <c r="M10" s="9"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="40"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="41"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
@@ -27009,17 +27035,17 @@
       <c r="D11" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E11" s="38"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="40"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="41"/>
       <c r="H11" s="7"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="40"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="41"/>
       <c r="K11" s="7"/>
-      <c r="L11" s="51"/>
+      <c r="L11" s="52"/>
       <c r="M11" s="7"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="40"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="41"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
@@ -27059,17 +27085,17 @@
       <c r="D12" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="40"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="41"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="40"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="41"/>
       <c r="K12" s="9"/>
-      <c r="L12" s="51"/>
+      <c r="L12" s="52"/>
       <c r="M12" s="9"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="40"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="41"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
@@ -27109,17 +27135,17 @@
       <c r="D13" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E13" s="38"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="40"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="41"/>
       <c r="H13" s="7"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="40"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="41"/>
       <c r="K13" s="7"/>
-      <c r="L13" s="51"/>
+      <c r="L13" s="52"/>
       <c r="M13" s="7"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="40"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="41"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -27159,17 +27185,17 @@
       <c r="D14" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E14" s="38"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="40"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="41"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="40"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="41"/>
       <c r="K14" s="9"/>
-      <c r="L14" s="51"/>
+      <c r="L14" s="52"/>
       <c r="M14" s="9"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="40"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="41"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
@@ -27209,17 +27235,17 @@
       <c r="D15" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E15" s="38"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="40"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="41"/>
       <c r="H15" s="7"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="40"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="41"/>
       <c r="K15" s="7"/>
-      <c r="L15" s="51"/>
+      <c r="L15" s="52"/>
       <c r="M15" s="7"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="40"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="41"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
@@ -27259,17 +27285,17 @@
       <c r="D16" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E16" s="38"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="41"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="40"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="41"/>
       <c r="K16" s="9"/>
-      <c r="L16" s="51"/>
+      <c r="L16" s="52"/>
       <c r="M16" s="9"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="40"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="41"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
@@ -27309,17 +27335,17 @@
       <c r="D17" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E17" s="38"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="40"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="41"/>
       <c r="H17" s="7"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="40"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="41"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="51"/>
+      <c r="L17" s="52"/>
       <c r="M17" s="7"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="40"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="41"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
@@ -27359,17 +27385,17 @@
       <c r="D18" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E18" s="38"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="40"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="41"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="40"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="41"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="51"/>
+      <c r="L18" s="52"/>
       <c r="M18" s="9"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="40"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="41"/>
       <c r="P18" s="9"/>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
@@ -27409,17 +27435,17 @@
       <c r="D19" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E19" s="38"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="40"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="41"/>
       <c r="H19" s="7"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="40"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="41"/>
       <c r="K19" s="7"/>
-      <c r="L19" s="51"/>
+      <c r="L19" s="52"/>
       <c r="M19" s="7"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="40"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="41"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
@@ -27459,17 +27485,17 @@
       <c r="D20" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="40"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="41"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="40"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="41"/>
       <c r="K20" s="9"/>
-      <c r="L20" s="51"/>
+      <c r="L20" s="52"/>
       <c r="M20" s="9"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="40"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="41"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
@@ -27509,17 +27535,17 @@
       <c r="D21" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E21" s="38"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="40"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="41"/>
       <c r="H21" s="7"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="40"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="41"/>
       <c r="K21" s="7"/>
-      <c r="L21" s="51"/>
+      <c r="L21" s="52"/>
       <c r="M21" s="7"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="40"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="41"/>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
@@ -27559,17 +27585,17 @@
       <c r="D22" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E22" s="38"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="40"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="41"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="40"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="41"/>
       <c r="K22" s="9"/>
-      <c r="L22" s="51"/>
+      <c r="L22" s="52"/>
       <c r="M22" s="9"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="40"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="41"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
@@ -27609,17 +27635,17 @@
       <c r="D23" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E23" s="38"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="40"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="41"/>
       <c r="H23" s="7"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="40"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="41"/>
       <c r="K23" s="7"/>
-      <c r="L23" s="51"/>
+      <c r="L23" s="52"/>
       <c r="M23" s="7"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="40"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="41"/>
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
@@ -27659,17 +27685,17 @@
       <c r="D24" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E24" s="38"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="40"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="41"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="40"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="41"/>
       <c r="K24" s="9"/>
-      <c r="L24" s="51"/>
+      <c r="L24" s="52"/>
       <c r="M24" s="9"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="40"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="41"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
@@ -27709,17 +27735,17 @@
       <c r="D25" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E25" s="38"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="40"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="41"/>
       <c r="H25" s="7"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="40"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="41"/>
       <c r="K25" s="7"/>
-      <c r="L25" s="51"/>
+      <c r="L25" s="52"/>
       <c r="M25" s="7"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="40"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="41"/>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
@@ -27759,17 +27785,17 @@
       <c r="D26" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E26" s="38"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="41"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="40"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="41"/>
       <c r="K26" s="9"/>
-      <c r="L26" s="51"/>
+      <c r="L26" s="52"/>
       <c r="M26" s="9"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="40"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="41"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
@@ -27809,17 +27835,17 @@
       <c r="D27" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E27" s="38"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="40"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="41"/>
       <c r="H27" s="7"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="40"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="41"/>
       <c r="K27" s="7"/>
-      <c r="L27" s="51"/>
+      <c r="L27" s="52"/>
       <c r="M27" s="7"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="40"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="41"/>
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
@@ -27859,17 +27885,17 @@
       <c r="D28" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E28" s="38"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="41"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="40"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="41"/>
       <c r="K28" s="9"/>
-      <c r="L28" s="51"/>
+      <c r="L28" s="52"/>
       <c r="M28" s="9"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="40"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="41"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
@@ -27909,17 +27935,17 @@
       <c r="D29" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E29" s="38"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="40"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="41"/>
       <c r="H29" s="7"/>
-      <c r="I29" s="38"/>
-      <c r="J29" s="40"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="41"/>
       <c r="K29" s="7"/>
-      <c r="L29" s="51"/>
+      <c r="L29" s="52"/>
       <c r="M29" s="7"/>
-      <c r="N29" s="38"/>
-      <c r="O29" s="40"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="41"/>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
@@ -27959,17 +27985,17 @@
       <c r="D30" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E30" s="38"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="40"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="41"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="38"/>
-      <c r="J30" s="40"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="41"/>
       <c r="K30" s="9"/>
-      <c r="L30" s="51"/>
+      <c r="L30" s="52"/>
       <c r="M30" s="9"/>
-      <c r="N30" s="38"/>
-      <c r="O30" s="40"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="41"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
@@ -28009,17 +28035,17 @@
       <c r="D31" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E31" s="38"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="40"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="41"/>
       <c r="H31" s="7"/>
-      <c r="I31" s="38"/>
-      <c r="J31" s="40"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="41"/>
       <c r="K31" s="7"/>
-      <c r="L31" s="51"/>
+      <c r="L31" s="52"/>
       <c r="M31" s="7"/>
-      <c r="N31" s="38"/>
-      <c r="O31" s="40"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="41"/>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
@@ -28059,17 +28085,17 @@
       <c r="D32" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E32" s="38"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="40"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="41"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="38"/>
-      <c r="J32" s="40"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="41"/>
       <c r="K32" s="9"/>
-      <c r="L32" s="51"/>
+      <c r="L32" s="52"/>
       <c r="M32" s="9"/>
-      <c r="N32" s="38"/>
-      <c r="O32" s="40"/>
+      <c r="N32" s="39"/>
+      <c r="O32" s="41"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
@@ -28109,17 +28135,17 @@
       <c r="D33" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="40"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="41"/>
       <c r="H33" s="7"/>
-      <c r="I33" s="38"/>
-      <c r="J33" s="40"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="41"/>
       <c r="K33" s="7"/>
-      <c r="L33" s="51"/>
+      <c r="L33" s="52"/>
       <c r="M33" s="7"/>
-      <c r="N33" s="38"/>
-      <c r="O33" s="40"/>
+      <c r="N33" s="39"/>
+      <c r="O33" s="41"/>
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
@@ -28159,17 +28185,17 @@
       <c r="D34" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E34" s="38"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="40"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="41"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="38"/>
-      <c r="J34" s="40"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="41"/>
       <c r="K34" s="9"/>
-      <c r="L34" s="51"/>
+      <c r="L34" s="52"/>
       <c r="M34" s="9"/>
-      <c r="N34" s="38"/>
-      <c r="O34" s="40"/>
+      <c r="N34" s="39"/>
+      <c r="O34" s="41"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
@@ -28209,17 +28235,17 @@
       <c r="D35" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E35" s="38"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="40"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="41"/>
       <c r="H35" s="7"/>
-      <c r="I35" s="38"/>
-      <c r="J35" s="40"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="41"/>
       <c r="K35" s="7"/>
-      <c r="L35" s="51"/>
+      <c r="L35" s="52"/>
       <c r="M35" s="7"/>
-      <c r="N35" s="38"/>
-      <c r="O35" s="40"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="41"/>
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
       <c r="R35" s="7"/>
@@ -28259,17 +28285,17 @@
       <c r="D36" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E36" s="38"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="40"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="41"/>
       <c r="H36" s="9"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="40"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="41"/>
       <c r="K36" s="9"/>
-      <c r="L36" s="51"/>
+      <c r="L36" s="52"/>
       <c r="M36" s="9"/>
-      <c r="N36" s="38"/>
-      <c r="O36" s="40"/>
+      <c r="N36" s="39"/>
+      <c r="O36" s="41"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="9"/>
       <c r="R36" s="9"/>
@@ -28309,17 +28335,17 @@
       <c r="D37" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E37" s="38"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="40"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="41"/>
       <c r="H37" s="7"/>
-      <c r="I37" s="38"/>
-      <c r="J37" s="40"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="41"/>
       <c r="K37" s="7"/>
-      <c r="L37" s="51"/>
+      <c r="L37" s="52"/>
       <c r="M37" s="7"/>
-      <c r="N37" s="38"/>
-      <c r="O37" s="40"/>
+      <c r="N37" s="39"/>
+      <c r="O37" s="41"/>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="7"/>
@@ -28359,17 +28385,17 @@
       <c r="D38" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="E38" s="41"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="43"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="44"/>
       <c r="H38" s="9"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="43"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="44"/>
       <c r="K38" s="9"/>
-      <c r="L38" s="52"/>
+      <c r="L38" s="53"/>
       <c r="M38" s="9"/>
-      <c r="N38" s="41"/>
-      <c r="O38" s="43"/>
+      <c r="N38" s="42"/>
+      <c r="O38" s="44"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="9"/>
       <c r="R38" s="9"/>
